--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -15,6 +15,7 @@
     <sheet name="机制词汇表" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="分布统计" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="经济基准" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="平衡旋钮清单" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'常规卡池'!$B$4:$J$49</definedName>
@@ -100,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -125,6 +126,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="B2:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -504,7 +514,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>赌徒 · 角色总览（§1）</t>
+          <t>赌徒 · 角色总览（§1 · 设计 v1.3）</t>
         </is>
       </c>
     </row>
@@ -560,20 +570,18 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="38" customHeight="1">
+    <row r="7" ht="70" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>起始金币</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
+      <c r="C7" s="3" t="n">
+        <v>148</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>原版标准，保持商店/删卡张力</t>
+          <t>高于原版（99）：混合费用需要更厚启动本金（设定：本该 150，当铺抽走两枚「手续费」）</t>
         </is>
       </c>
     </row>
@@ -625,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="B2:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -661,7 +669,7 @@
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>幸运筹码（初始遗物）</t>
         </is>
@@ -673,14 +681,14 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>事后改一掷为正面，每回合 1 次</t>
+          <t>事后改一掷为正面，每回合 1 次（花 5 金币）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>换骰</t>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>暗记</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -690,73 +698,39 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>重掷本回合一枚已掷出的硬币</t>
+          <t>下一次赌博必为正面</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>暗记</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>手气正旺</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>罕见技</t>
+          <t>罕见能力</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>下一次赌博必为正面</t>
+          <t>正面率 +15%（常驻）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>操纵牌局</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>赌神</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>稀有技</t>
+          <t>稀有能力</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>重掷本回合全部已掷出的硬币</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>手气正旺</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>罕见能力</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>正面率 +15%（常驻）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>赌神</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>稀有能力</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>所有赌博视为正面</t>
         </is>
@@ -776,7 +750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="B2:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -921,7 +895,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1 能</t>
+          <t>0 能</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -931,12 +905,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>获得 4 金币</t>
+          <t>获得 5 金币</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>获得 6 金币</t>
+          <t>获得 7 金币</t>
         </is>
       </c>
     </row>
@@ -978,7 +952,7 @@
     <row r="10" ht="34" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>两张签名牌让"产金"和"赌博"从第一回合就在场。私房钱 1 能换 4 金即时展示补贴率（金印价的 1.33 倍）；试手气即赌博模板的教学样板。</t>
+          <t>两张签名牌让"产金"和"赌博"从第一回合就在场。私房钱 0 能白拿 5 金——产金基准（1 能量 = 7 金币）的免能量特例；试手气即赌博模板的教学样板。</t>
         </is>
       </c>
     </row>
@@ -997,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="B2:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1016,7 +990,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>常规卡池 · 45 张（普 11 / 罕 20 / 稀 14 · §5.1–5.3）</t>
+          <t>常规卡池 · 43 张（普 11 / 罕 19 / 稀 13 · §5.1–5.3）</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1053,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>飞牌</t>
+          <t>底注</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1104,12 +1078,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>造成 9 伤害</t>
+          <t>造成 10 伤害</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>造成 12 伤害</t>
+          <t>造成 13 伤害</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1123,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>造成 6 伤害。可额外花费至多 6 金币，每 1 金币 +1 伤害</t>
+          <t>造成 6 伤害。可额外花费至多 6 金币，每 1 金币 +2 伤害</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -1169,7 +1143,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>赌一把</t>
+          <t>买定离手</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1214,7 +1188,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>打手</t>
+          <t>看场</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1239,12 +1213,12 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>造成 8 伤害，施加 1 易伤</t>
+          <t>造成 16 伤害，施加 1 易伤</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>11 伤害，2 易伤</t>
+          <t>19 伤害，2 易伤</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1233,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>赏金猎人</t>
+          <t>悬红</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1284,12 +1258,12 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>造成 7 伤害。击杀则获得 8 金币</t>
+          <t>造成 7 伤害。击杀则获得 10 金币</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>9 伤害，击杀 +12 金</t>
+          <t>9 伤害，击杀 +14 金</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1278,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>零钱</t>
+          <t>筹码</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1314,7 +1288,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1324,17 +1298,17 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>免费产金</t>
+          <t>小额产金·基准</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>获得 3 金币</t>
+          <t>获得 7 金币</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>获得 5 金币</t>
+          <t>获得 9 金币</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1323,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>买平安</t>
+          <t>护盘</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1374,12 +1348,12 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>获得 11 格挡</t>
+          <t>获得 15 格挡</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>获得 14 格挡</t>
+          <t>获得 18 格挡</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1368,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>灵光一闪</t>
+          <t>盲注</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1439,7 +1413,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>买路钱</t>
+          <t>摸牌</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1464,12 +1438,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>抽 2 张牌</t>
+          <t>抽 3 张牌</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张牌</t>
+          <t>抽 4 张牌</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1458,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>下绊子</t>
+          <t>放水</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1509,12 +1483,12 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>施加 2 虚弱</t>
+          <t>施加 4 虚弱</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>施加 3 虚弱</t>
+          <t>施加 5 虚弱</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1503,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>存钱罐</t>
+          <t>返水</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1554,12 +1528,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>每回合开始获得 2 金币</t>
+          <t>每回合开始获得 3 金币</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>每回合 3 金币</t>
+          <t>每回合 4 金币</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1573,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>造成 10×X 伤害</t>
+          <t>造成 27×X 伤害</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1664,7 +1638,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>洗劫★</t>
+          <t>清台★</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1689,12 +1663,12 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>对所有敌人造成 5 伤害。每击杀一个敌人，获得 5 金币</t>
+          <t>对所有敌人造成 13 伤害。每击杀一个敌人，获得 7 金币</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>造成 7 伤害</t>
+          <t>造成 15 伤害</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1748,12 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>上一掷联动</t>
+          <t>倍率条件</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>造成 8 伤害。若你的上一掷为正面，改为 16 伤害</t>
+          <t>造成 8 伤害。若倍率 ≥1.5，改为 16 伤害</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1824,12 +1798,12 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>造成 8 伤害。赌博：正面 → 改为 16 伤害</t>
+          <t>造成 10 伤害。赌博：正面 → 改为 20 伤害</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>11 / 正面 21</t>
+          <t>13 / 正面 25</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1863,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>雇佣打手</t>
+          <t>摇骰</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1914,12 +1888,12 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>对随机敌人造成 4 伤害 3 次。赌博：正面 → 每次 7</t>
+          <t>对随机敌人造成 4 伤害 3 次。赌博：正面 → 每次 9</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>5×3 / 正面每次 8</t>
+          <t>5×3 / 正面每次 10</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1908,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>换骰</t>
+          <t>暗记</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1954,17 +1928,17 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>做局·重掷一枚</t>
+          <t>做局·下一掷必正</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>重掷本回合一枚已掷出的硬币</t>
+          <t>你的下一次赌博必为正面</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>费用变为 0</t>
+          <t>接下来 2 次必为正面</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1953,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>暗记</t>
+          <t>派彩</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1989,7 +1963,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+3金</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1999,21 +1973,21 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>做局·下一掷必正</t>
+          <t>投资回本</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>你的下一次赌博必为正面</t>
+          <t>获得 18 金币，抽 1 张牌</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>接下来 2 次必为正面</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
+          <t>获得 22 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1">
       <c r="B26" s="6" t="n">
         <v>22</v>
       </c>
@@ -2024,7 +1998,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>分红</t>
+          <t>数牌★</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2034,7 +2008,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2能+3金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -2044,17 +2018,17 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>投资回本</t>
+          <t>算牌·信息优势</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>获得 10 金币，抽 1 张牌</t>
+          <t>查看抽牌堆顶 3 张，可将其中任意张置入弃牌堆</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>获得 14 金币</t>
+          <t>顶 4 张</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2043,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>数牌★</t>
+          <t>兑筹★</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2079,7 +2053,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2089,17 +2063,17 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>算牌·信息优势</t>
+          <t>牌换金·卡组精简</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>查看抽牌堆顶 3 张，可将其中任意张置入弃牌堆</t>
+          <t>消耗手牌 1 张，获得 12 金币</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>顶 4 张</t>
+          <t>获得 16 金币</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2088,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>当铺★</t>
+          <t>抽头</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2129,22 +2103,22 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>牌换金·卡组精简</t>
+          <t>赌博·产金</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>消耗手牌 1 张，获得其价值：基础 3 / 普通 5 / 罕见 8 / 稀有 12 金币</t>
+          <t>获得 7 金币。赌博：正面 → 改为 14 金币</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>金额 +2</t>
+          <t>9 / 正面 18</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2133,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>抽头</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2169,7 +2143,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2179,21 +2153,21 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>赌博·产金</t>
+          <t>反向赌博（盼反面）</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>获得 6 金币。赌博：正面 → 改为 11 金币</t>
+          <t>获得 8 格挡。赌博：反面 → 改为 16 格挡</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>8 / 正面 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="38" customHeight="1">
+          <t>10 / 反面 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
       <c r="B30" s="6" t="n">
         <v>26</v>
       </c>
@@ -2204,7 +2178,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>假筹</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2214,31 +2188,31 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>反向赌博（盼反面）</t>
+          <t>金币费用豁免</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>获得 6 格挡。赌博：反面 → 改为 13 格挡</t>
+          <t>你的下一次金币花费不消耗金币</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>8 / 反面 18</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
+          <t>本场战斗前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="38" customHeight="1">
       <c r="B31" s="5" t="n">
         <v>27</v>
       </c>
@@ -2249,7 +2223,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>假币</t>
+          <t>高利贷★</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2259,7 +2233,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2269,21 +2243,21 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>金币费用豁免</t>
+          <t>跨战斗贷款</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>你的下一次金币花费不消耗金币</t>
+          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>本场战斗前 2 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="38" customHeight="1">
+          <t>获得 18 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
       <c r="B32" s="6" t="n">
         <v>28</v>
       </c>
@@ -2294,17 +2268,17 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>高利贷★</t>
+          <t>手气正旺</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>0能</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2314,21 +2288,21 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>跨战斗贷款</t>
+          <t>做局·被动概率</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>获得 12 金币。下场战斗开始时失去 6 金币（不足则全失）</t>
+          <t>赌博正面率 +15%</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>获得 16 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
+          <t>+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="38" customHeight="1">
       <c r="B33" s="5" t="n">
         <v>29</v>
       </c>
@@ -2339,7 +2313,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>手气正旺</t>
+          <t>台规</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2359,21 +2333,21 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>做局·被动概率</t>
+          <t>收入×正面联动</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>赌博正面率 +15%</t>
+          <t>每回合开始获得 4 金币；每次掷出正面，额外获得 3 金币</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="38" customHeight="1">
+          <t>每回合 5 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
       <c r="B34" s="6" t="n">
         <v>30</v>
       </c>
@@ -2384,7 +2358,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>赌场规则</t>
+          <t>流水</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -2394,7 +2368,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -2404,62 +2378,62 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>收入×正面联动</t>
+          <t>花费追踪·转抽牌</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>每回合开始获得 3 金币；每次掷出正面，额外获得 2 金币</t>
+          <t>你每累计花费 10 金币，抽 1 张牌</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>每回合 4 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
+          <t>每累计 8 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1">
       <c r="B35" s="5" t="n">
         <v>31</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>流水</t>
+          <t>孤注一掷</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+10金</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔真赌</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>花费追踪·转抽牌</t>
+          <t>真赌·尖刺</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>你每累计花费 10 金币，抽 1 张牌</t>
+          <t>造成 27 伤害。赌博：正面 → 改为 43 伤害；反面 → 改为 25 伤害且自己受到 6 伤害</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>每累计 8 金币</t>
+          <t>正面 50 / 反面 29</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2448,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>孤注一掷</t>
+          <t>俄罗斯轮盘</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -2484,7 +2458,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>1能+10金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2494,21 +2468,21 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>真赌·尖刺</t>
+          <t>真赌·自伤多段</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>造成 12 伤害。赌博：正面 → 改为 28 伤害；反面 → 改为 9 伤害且自己受到 6 伤害</t>
+          <t>对随机敌人造成 3 伤害 5 次。赌博：正面 → 每次改为 5；反面 → 其中 2 发改为打自己（自己共受 10 伤害）</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>正面 34 / 反面 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="54" customHeight="1">
+          <t>每次 4 / 正面 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
       <c r="B37" s="5" t="n">
         <v>33</v>
       </c>
@@ -2519,7 +2493,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>俄罗斯轮盘</t>
+          <t>爆机</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2529,31 +2503,31 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>3能+8金</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>✔真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>真赌·自伤多段</t>
+          <t>头奖·击杀产金大</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>对随机敌人造成 3 伤害 5 次。赌博：正面 → 每次改为 5；反面 → 其中 2 发改为打自己（自己共受 10 伤害）</t>
+          <t>造成 35 伤害。击杀则获得 25 金币</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>每次 4 / 正面 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
+          <t>40 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="38" customHeight="1">
       <c r="B38" s="6" t="n">
         <v>34</v>
       </c>
@@ -2564,7 +2538,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>贪婪重击</t>
+          <t>豹子</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -2574,27 +2548,27 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>3能+8金</t>
+          <t>2能+10金</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔×3</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>头奖·击杀产金大</t>
+          <t>赌博·逐击独立</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>造成 20 伤害。击杀则获得 20 金币</t>
+          <t>造成 9 伤害 3 次，每击独立赌博：正面则该击改为 18</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>26 伤害</t>
+          <t>每击 10 / 正面 20</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2583,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>同花顺</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2619,27 +2593,27 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>3能+12金</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>✔×3</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>赌博·逐击独立</t>
+          <t>兑现·终结</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>造成 5 伤害 3 次，每击独立赌博：正面则该击改为 12</t>
+          <t>造成 43 伤害 ×倍率</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>每击 6 / 正面 13</t>
+          <t>46 伤害</t>
         </is>
       </c>
     </row>
@@ -2654,37 +2628,37 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>同花顺</t>
+          <t>单双</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>3能+12金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔真赌</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>正面计数终结</t>
+          <t>真赌·能量</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>造成 30 伤害。若本回合你掷出过 ≥3 次正面，改为 45 伤害</t>
+          <t>赌博：正面 → 获得 4 点能量；反面 → 失去 1 点能量</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>36 / 54</t>
+          <t>正面 5 点能量</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2673,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>天命</t>
+          <t>老虎机</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2709,31 +2683,31 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+5金</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>✔真赌</t>
+          <t>✔×3</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>真赌·能量</t>
+          <t>头奖·多次掷产金引擎</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>赌博：正面 → 获得 4 点能量；反面 → 失去 1 点能量</t>
+          <t>赌博 3 次，每次正面：获得 9 金币并抽 1 张牌</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>正面 5 点能量</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="38" customHeight="1">
+          <t>每次正面 11 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
       <c r="B42" s="6" t="n">
         <v>38</v>
       </c>
@@ -2744,7 +2718,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>老虎机</t>
+          <t>打庄★</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -2754,27 +2728,27 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2能+5金</t>
+          <t>2能+15金</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>✔×3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>头奖·多次掷产金引擎</t>
+          <t>定向斩杀（最低生命）</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>赌博 3 次，每次正面：获得 7 金币并抽 1 张牌</t>
+          <t>对生命值最低的敌人造成 43 伤害</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>每次正面 9 金币</t>
+          <t>50 伤害</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2763,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>操纵牌局</t>
+          <t>弃牌</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2799,31 +2773,31 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2能+6金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>消耗</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>做局·全重掷</t>
+          <t>自消耗换值</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>重掷本回合全部已掷出的硬币</t>
+          <t>抽 2 张牌，获得 14 金币</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>费用变为 1 能+6 金</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
+          <t>抽 3 张，18 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="38" customHeight="1">
       <c r="B44" s="6" t="n">
         <v>40</v>
       </c>
@@ -2834,7 +2808,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>买凶★</t>
+          <t>抽佣★</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -2844,7 +2818,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2能+15金</t>
+          <t>2能+8金</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2854,21 +2828,21 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>定向斩杀（最低生命）</t>
+          <t>力量剥夺</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>对生命值最低的敌人造成 30 伤害</t>
+          <t>施加 5 点力量削弱与 3 易伤</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>40 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
+          <t>6 点力量削弱与 4 易伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="38" customHeight="1">
       <c r="B45" s="5" t="n">
         <v>41</v>
       </c>
@@ -2879,7 +2853,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>撕毁契约</t>
+          <t>底牌</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2894,26 +2868,26 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>消耗</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>自消耗换值</t>
+          <t>倍率条件·抽牌</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>抽 2 张牌，获得 12 金币</t>
+          <t>抽 2 张牌。若倍率 ≥1.5，额外抽 1 张牌</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张，16 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="38" customHeight="1">
+          <t>抽 3 张牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
       <c r="B46" s="6" t="n">
         <v>42</v>
       </c>
@@ -2924,17 +2898,17 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>黑吃黑★</t>
+          <t>赌神</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>3能</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -2944,17 +2918,17 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>力量剥夺</t>
+          <t>做局·终极全正</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>施加 3 点力量削弱与 2 易伤</t>
+          <t>你的所有赌博视为正面</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>4 点力量削弱与 3 易伤</t>
+          <t>费用变为 2</t>
         </is>
       </c>
     </row>
@@ -2969,166 +2943,1761 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>底牌</t>
+          <t>利滚利★</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>产金放大器</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>本场战斗中你每次获得金币时，额外获得 2 金币</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>额外 3 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>收手</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>做局联动爆发</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>抽 2 张牌。若本回合掷出过正面，这些牌本回合费用 -1</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>抽 3 张牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>赌神</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>3能</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>做局·终极全正</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>你的所有赌博视为正面</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>费用变为 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="38" customHeight="1">
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>兑现·格挡</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>获得 5 格挡 ×倍率</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>8 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
       <c r="B49" s="5" t="n">
         <v>45</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>乘胜</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>兑现·单体</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>造成 6 伤害 ×倍率</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>9 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>割禾青</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>倍率折算·抽牌</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>每 0.5 倍率抽 1 张牌（至多 3 张）</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>至多 4 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>兑现</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>兑现·产金</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>获得 7 金币 ×倍率</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="B52" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>通杀</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>2能+5金</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>兑现·AoE</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>对所有敌人造成 16 伤害 ×倍率</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>20 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="54" customHeight="1">
+      <c r="B53" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>利滚利★</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>晒冷</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>3能+15金</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>兑现·大炮</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>造成 50 伤害 ×倍率</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>62 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="54" customHeight="1">
+      <c r="B54" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>追数</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>2能+8金</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>兑现·击杀续风</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>造成 29 伤害 ×倍率；若击杀则本次不清空倍率</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>36 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="54" customHeight="1">
+      <c r="B55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>割肉</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>兑现·自伤</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>获得 10 格挡 ×倍率；自身失去「倍率 ×3」生命</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>13 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="B56" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>散码</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>即时产金·弃牌堆</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8）</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>至多 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>买码</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>即时产金·敌人数</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>每个敌人给予 5 金币</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>每敌人 7 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>吃水</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>1能+4金</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>击杀产金·溢出转金</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>造成 12 伤害；**溢出的伤害**转为金币</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>16 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="B59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>点码</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>花费追踪·转格挡</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>获得 5 格挡；本回合每花费过 5 金币，额外 +3 格挡</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>每 5 金 +4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>洗牌</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>弃牌换抽</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>弃置 1 张手牌，抽 2 张牌</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>抽 3 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>护池</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>1能+4金</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>附加费·多段格挡</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>获得 5 格挡 3 次</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>7 格挡 3 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="B62" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>换码</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>0能+6金</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>附加费·买能量</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>获得 2 点能量</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>获得 3 点</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="B63" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>再加注</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>可变投入·档位解锁</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>自动花费至多 9 金：造成 8 伤害；≥3 金另施加 2 易伤；≥6 金另抽 1 张；≥9 金再 +8 伤害</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="B64" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>抽水</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>即时产金·手牌数</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>每张手牌获得 1 金币（至多 8）</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>至多 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="B65" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>押宝</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>1能+5金</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>✔真赌</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>真赌·押 HP</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>造成 18 伤害。赌博：正面 → 25 伤害；反面 → 自己失去 6 点生命</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>24 / 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="B66" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>反水</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>1能+2金</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>赌博·格挡反击</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>赌博：正面 → 获得 9 格挡并造成 9 伤害；反面 → 获得 5 格挡</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>11 / 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="B67" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>叠码</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>做局·倍率注入</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>倍率 +1.0</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>倍率 +1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="B68" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>保底</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>消耗堆协同·格挡</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>获得 10 格挡；每张**已消耗**的牌 +2 格挡（至多 +10）</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>12 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="B69" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>加码</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>花费追踪·转能量</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>获得 1 点能量；本回合每花费过 10 金，额外 +1（至多 3）</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>每 8 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="B70" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>清码</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>手牌换金</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>弃置全部手牌，每弃 1 张获得 4 金币</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>每张 5 金</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="B71" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>翻盘</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>1能+3金</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>生命条件</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>造成 10 伤害；若你的生命低于 50%，改为 24 伤害</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>14 / 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="B72" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>暗注</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>1能+6金</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>附加费·穿透</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>造成 6 点**无视格挡**的伤害</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>9 点</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="B73" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>连庄</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>✔×3</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>赌博·累积多掷</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>掷硬币 3 次，每次正面获得 8 格挡</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>每次 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="B74" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>抵押</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>产金放大器</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>本场战斗中你每次获得金币时，额外获得 1 金币</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>额外 2 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>费用列简写："1能+5金" = 1 能量 + 5 金币；赌博列"✔"表示带赌博词条，真赌标注反面惩罚；★ = v1.2 新钩子卡；效果列均为参考数值，可直接改。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="B52" s="7" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>特异·卖血换甲</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>获得 12 格挡；自己失去 4 点生命</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>16 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="B75" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>换牌</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>特异·消耗换抽</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>消耗 1 张手牌，抽 2 张牌</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>抽 3 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="54" customHeight="1">
+      <c r="B76" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>全下</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>X能+7X金</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>附加费·X费多段</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>对随机敌人造成 9×X 伤害，共 X 次</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>金币费降为 5×X</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="54" customHeight="1">
+      <c r="B77" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>出千</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>做局·本回合全正</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>本回合你接下来的所有赌博必为正面</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>费用变为 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="54" customHeight="1">
+      <c r="B78" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>摊牌</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>特异·弃牌堆规模</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>对随机敌人造成「弃牌堆张数」伤害（至多 20）</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>至多 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="54" customHeight="1">
+      <c r="B79" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>保本</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>2能+10金</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>特异·金币转格挡</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>消耗你一半金币，获得等量格挡（至多 30）</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>至多 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="54" customHeight="1">
+      <c r="B80" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>押牌</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>✔真赌</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>真赌·押手牌</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>造成 8 伤害。赌博：正面 → 15 伤害；反面 → 弃掉 2 张手牌</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>12 / 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="54" customHeight="1">
+      <c r="B81" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>截胡</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>2能+8金</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>击杀产金·处决</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>26 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="54" customHeight="1">
+      <c r="B82" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>倍投</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>做局·倍率翻倍</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>你的倍率**翻倍**</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>费用变为 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="54" customHeight="1">
+      <c r="B83" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>换筹</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>风头·兑现能量</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>按倍率折算能量：获得「倍率取整」点能量，结算后清空</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>+1 点</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="54" customHeight="1">
+      <c r="B84" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>满贯</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>2能+18金</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>特异·赌博计数</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>造成 30 伤害；若本场战斗中你掷出过正面，改为 50 伤害</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>38 / 62</t>
+        </is>
+      </c>
+    </row>
+    <row r="85"/>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>费用列简写："1能+5金" = 1 能量 + 5 金币；赌博列"✔"表示带赌博词条（"风头"= 带「风头正盛」词条，v1.6 新增），真赌标注反面惩罚；★ = v1.2 新钩子卡；效果列均已按当前代码实装校对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
         <is>
           <t>v1.2 重设计原则：一张卡 = 一个钩子。消灭纯数值变体，每张卡在"钩子"列声明其独有机制，同家族不重复占位。</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="B53" s="7" t="inlineStr">
+    <row r="88">
+      <c r="B88" t="inlineStr">
         <is>
           <t>v1.2 替换记录：三连骰→洗劫、出老千→叠注、催债人→连胜、铁赌桌→当铺、脚底抹油→高利贷、切牌→数牌、金库→买凶、威逼利诱→黑吃黑、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="B54" s="7" t="inlineStr">
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>v1.3 评审删除：「换骰」「操纵牌局」——不做重掷机制，删后不补新卡（卡池 45→43，编号已重排，见设计文档 §5）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>实装同步注记（以代码为准）：加注为自动花费至多 6 金币（选额 UI 留美术资产批）；数牌为选 1 张置入弃牌堆；底牌正面改为额外抽 1 张（原设计"费用 -1"待费用修改器接入后还原）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
         <is>
           <t>注：「保险」是反向赌博（反面才强化），全池唯一一张"盼反面"的普通赌博牌，为真赌牌和做局留心理准备。</t>
         </is>
       </c>
     </row>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
   </sheetData>
   <autoFilter ref="B4:J49"/>
-  <mergeCells count="5">
-    <mergeCell ref="B51:J51"/>
-    <mergeCell ref="B53:J53"/>
+  <mergeCells count="7">
+    <mergeCell ref="B90:J90"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="B88:J88"/>
     <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B52:J52"/>
-    <mergeCell ref="B54:J54"/>
+    <mergeCell ref="B91:J91"/>
+    <mergeCell ref="B86:J86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3140,7 +4709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="B2:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3329,27 +4898,27 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>8 伤</t>
+          <t>10 伤</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>16 伤</t>
+          <t>20 伤</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>10 伤（1能+3金）</t>
+          <t>12.3 伤（1能+3金@2.1）</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
     </row>
@@ -3366,22 +4935,22 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>7×3</t>
+          <t>9×3</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>13.5 伤（1能+5金）</t>
+          <t>16.5 伤（1能+5金@2.1）</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.18</t>
         </is>
       </c>
     </row>
@@ -3393,27 +4962,27 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>6 金</t>
+          <t>7 金</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>11 金</t>
+          <t>14 金</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>8.5 金</t>
+          <t>10.5 金</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>7 金（1 能罕档产金）</t>
+          <t>7 金（1 能产金基准）</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
@@ -3425,27 +4994,27 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>6 挡（正面）</t>
+          <t>8 挡（正面）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>13 挡（反面）</t>
+          <t>16 挡（反面）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>8 挡（1能+2金）</t>
+          <t>10 挡（1能+2金@2.5）</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.20</t>
         </is>
       </c>
     </row>
@@ -3489,27 +5058,27 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>5/击</t>
+          <t>9/击</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>12/击</t>
+          <t>18/击</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>21 伤（2能+10金）</t>
+          <t>33 伤（2能+10金@2.1）</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.23</t>
         </is>
       </c>
     </row>
@@ -3526,12 +5095,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7 金+抽 1/掷</t>
+          <t>9 金+抽 1/掷</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>≈13.5 金当量</t>
+          <t>≈15 金当量</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -3541,7 +5110,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>≈1.2</t>
+          <t>≈1.3</t>
         </is>
       </c>
     </row>
@@ -3553,22 +5122,22 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>9 伤+自伤 6</t>
+          <t>25 伤+自伤 6</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>28 伤</t>
+          <t>43 伤</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>≈17</t>
+          <t>≈32.5</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>14 伤（1能+10金）</t>
+          <t>27 伤（1能+10金@2.1）</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -3687,7 +5256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="B2:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3730,12 +5299,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>伤（飞牌）/ 格挡（买平安）/ 抽牌（买路钱）/ 纯 debuff（下绊子）/ 伤+debuff（打手）</t>
+          <t>伤（底注）/ 格挡（护盘）/ 抽牌（摸牌）/ 纯 debuff（放水）/ 伤+debuff（看场）/ 多段格挡（护池）/ 买能量（换码）/ 穿透（暗注）</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>多段附加费、附加费买能量</t>
+          <t>多段伤、附加费买遗物、附加费转抽牌</t>
         </is>
       </c>
     </row>
@@ -3747,12 +5316,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>小额封顶（加注）/ X 费炮（梭哈）</t>
+          <t>小额封顶（加注）/ X 费炮（梭哈）/ X 费多段（全下）/ 档位解锁（再加注）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>按投入档位解锁额外效果</t>
+          <t>按投入档位改目标数</t>
         </is>
       </c>
     </row>
@@ -3764,12 +5333,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>单体（赏金猎人）/ AoE（洗劫）/ 大额头奖（贪婪重击）</t>
+          <t>单体（悬红）/ AoE（清台）/ 大额头奖（爆机）/ 溢出转金（吃水）/ 处决（截胡）</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>溢出伤害按比例转金</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3781,12 +5350,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>免费（零钱）/ 投资回本（分红）/ 掷币（抽头）/ 牌换金（当铺）/ 贷款（高利贷）</t>
+          <t>基准（筹码）/ 免能量（本钱）/ 投资回本（派彩）/ 掷币（抽头）/ 牌换金（兑筹）/ 贷款（高利贷）/ 弃牌堆（散码）/ 敌人数（买码）/ 手牌数（抽水）/ 手牌换金（清码）</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>按弃牌堆张数、按敌人数产金</t>
+          <t>按生命值、按回合数</t>
         </is>
       </c>
     </row>
@@ -3798,12 +5367,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>定额（存钱罐）/ 正面触发（赌场规则）/ 增幅（利滚利）</t>
+          <t>定额（返水）/ 正面触发（台规）/ 增幅（利滚利）</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>回合结束结息</t>
+          <t>回合结束结息（**缺回合结束钩子，待补**）</t>
         </is>
       </c>
     </row>
@@ -3815,7 +5384,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>转伤害（连续下注）/ 转抽牌（流水）</t>
+          <t>转伤害（连续下注）/ 转抽牌（流水）/ 转格挡（点码）/ 转能量（加码）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -3832,7 +5401,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>基础（试手气）/ AoE（赌一把）/ 格挡（灵光一闪）/ 双段（双倍下注）/ 尖刺（翻本）/ 连锁（连胜）/ 逐击（豹子）/ 随机多段（雇佣打手）/ 反向（保险）</t>
+          <t>基础（试手气）/ AoE（买定离手）/ 格挡（盲注）/ 双段（双倍下注）/ 尖刺（翻本）/ 连锁（连胜）/ 逐击（豹子）/ 随机多段（摇骰）/ 反向（保险）/ 累积多掷（连庄）/ 格挡反击（反水）</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -3841,7 +5410,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="54" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>做局</t>
@@ -3849,12 +5418,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>单重掷（换骰）/ 全重掷（操纵牌局）/ 必正（暗记）/ 被动概率（手气正旺）/ 终极全正（赌神）/ 联动爆发（底牌）</t>
+          <t>必正（暗记）/ 被动概率（手气正旺）/ 终极全正（赌神）/ 倍率注入（叠码）/ 倍率翻倍（倍投）/ 本回合全正（出千）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>预知下一掷结果（信息做局）</t>
+          <t>预知下一掷（**需 Core 暴露预览，待补**）。~~重掷~~（v1.3 评估移除）</t>
         </is>
       </c>
     </row>
@@ -3866,27 +5435,44 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>尖刺（孤注一掷）/ 自伤多段（俄罗斯轮盘）/ 能量（天命）</t>
+          <t>尖刺（孤注一掷）/ 自伤多段（俄罗斯轮盘）/ 能量（单双）/ 押 HP（押宝）/ 押手牌（押牌）</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>押 HP、押手牌</t>
+          <t>押遗物</t>
         </is>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>风头正盛（兑现倍率，v1.6）</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>兑现·格挡（收手）/ 单体（乘胜）/ 产金（兑现）/ AoE（通杀）/ 大炮（晒冷）/ 击杀续风（追数）/ 自伤（割肉）/ 终结（同花顺）/ 折算·抽牌（割禾青）/ 折算·能量（换筹）/ 只读条件（叠注、底牌）</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>兑换成费用减免、倍率解锁机制</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
           <t>特异</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>费用豁免（假币）/ 自消耗换值（撕毁契约）/ 信息（数牌）/ 定向斩杀（买凶）/ 力量剥夺（黑吃黑）/ 上一掷联动（叠注）</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>费用豁免（假筹）/ 自消耗换值（弃牌）/ 信息（数牌）/ 定向斩杀（打庄）/ 力量剥夺（抽佣）/ 弃牌换抽（洗牌）/ 消耗换抽（换牌）/ 消耗堆协同·格挡（保底）/ 生命条件（翻盘）/ 卖血换甲（抵押）/ 金币转格挡（保本）/ 弃牌堆规模（摊牌）/ 赌博计数（满贯）</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>商店/遗物联动、跨战斗状态</t>
         </is>
@@ -3902,14 +5488,14 @@
     <row r="17" ht="34" customHeight="1">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>空白模板（复制到对应档位表末尾）：| — | （新卡名） | 攻/技/能 | X能+Y金 | ✔/— | （一句话钩子） | （效果） | （升级后） |</t>
+          <t>空白模板（复制到对应档位表末尾）：| — | （新卡名） | 攻/技/能 | X能+Y金 | ✔/风头/— | （一句话钩子） | （效果） | （升级后） |</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3922,7 +5508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="B2:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3963,7 +5549,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
+    <row r="5" ht="38" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>总卡数（常规）</t>
@@ -3971,12 +5557,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>80（v1.3 删 2 后 43；v1.6 +8 到 51；v1.7 +29 补齐模板）</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3993,12 +5579,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>11 普 / 20 罕 / 14 稀</t>
+          <t>20 普 / 35 罕 / 25 稀</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>11 / 20 / 14（按原版 25%/44%/31% 等比）</t>
+          <t>20 / 35 / 25（对齐原版模板）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -4015,21 +5601,21 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>≈18 攻 / 21 技 / 6 能</t>
+          <t>同原版比例</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>18 / 21 / 6</t>
+          <t>32 攻 / 42 技 / 6 能（v1.7 防御向：4 张攻击牌转格挡，格挡牌 9→13）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
+          <t>≈</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>金币直接费用</t>
@@ -4042,7 +5628,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>18：双费 17（普5/罕5/稀7）＋可变投入·加注</t>
+          <t>17：双费 16（普5/罕5/稀6）＋可变投入·加注</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -4064,12 +5650,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>14（起始1/普2/罕6/稀5；v1.2 新增连胜）</t>
+          <t>18（起始1/普3/罕8/稀6）</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>≈</t>
         </is>
       </c>
     </row>
@@ -4086,7 +5672,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>10（私房钱/零钱/赏金/洗劫/分红/抽头/当铺/高利贷/贪婪/老虎机；v1.2 上调）</t>
+          <t>14（v1.7 新增 零钱堆/人头费/抽水/收账）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -4130,12 +5716,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>3（孤注一掷/俄罗斯轮盘/天命）</t>
+          <t>5（+孤注/押牌）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>≈</t>
         </is>
       </c>
     </row>
@@ -4161,7 +5747,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="38" customHeight="1">
+    <row r="14" ht="54" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
           <t>做局工具</t>
@@ -4174,10 +5760,32 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>7（遗物/换骰/暗记/操纵牌局/手气正旺/赌神/底牌-条件）</t>
+          <t>8（+蓄风/加倍/出千）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>风头正盛（倍率）</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10 挂词条（9 + 兑筹码）＋ 2 只读条件（叠注/底牌）</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -4197,7 +5805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="B2:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4417,4 +6025,178 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="32" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>平衡旋钮清单——调平衡先动这些（§7.3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>旋钮</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>当前值</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>初始遗物改币价格</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>5 金 / 次，每回合限 1 次</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>最敏感的旋钮，直接决定赌博牌的等效确定性</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>双费卡补贴率</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>统一 1 能量 = 7 金币</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>能量↔金币换算基准（§2.1）；取代原分档口径 普4-6/罕5-10/稀8-15 金 ≈ 1 能量档</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>即时产金量级</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>单张 5-18 金；引擎 3-5 金/回合 + 正面触发</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>产金节奏与经济画像（§2.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>赌博期望锚定</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>反面 ≈ 白板 ×0.8 / 正面 ≈ ×1.6，E = 1.2×（0.8+0.8p）</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>动它牵动全部 14 张赌博牌，逐卡见 §5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>做局数值上限</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>正面率加法叠加，上限 75%</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>手气正旺 / 赌神的获取难度与数值上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>梭哈 X 金币系数</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>10×X</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>爆发上限的主要阀门</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>倍率成长步长 / 风头牌裸值</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>+0.5/次正面；裸值 = 白板</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>动它平移全部 11 张倍率关联牌；倍率不设上限（含金币）已定，经济风险已接受（§2.8）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>调平衡时动的第一批螺丝，对应设计文档 §7.3；改数值只动卡文件（GamblerMod/src/Cards/），Core 层不动。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>赌徒 · 角色总览（§1 · 设计 v1.3）</t>
+          <t>赌徒 · 角色总览（§1 · 设计 v1.7）</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>高于原版（99）：混合费用需要更厚启动本金（设定：本该 150，当铺抽走两枚「手续费」）</t>
+          <t>高于原版（99）：混合费用需要更厚启动本金（设定：本该 150，兑筹抽走两枚「手续费」）</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -750,7 +750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>私房钱</t>
+          <t>本钱</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -949,10 +949,11 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="34" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>两张签名牌让"产金"和"赌博"从第一回合就在场。私房钱 0 能白拿 5 金——产金基准（1 能量 = 7 金币）的免能量特例；试手气即赌博模板的教学样板。</t>
+          <t>两张签名牌让"产金"和"赌博"从第一回合就在场。本钱 0 能白拿 5 金——产金基准（1 能量 = 7 金币）的免能量特例；试手气即赌博模板的教学样板。</t>
         </is>
       </c>
     </row>
@@ -971,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J94"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -990,7 +991,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>常规卡池 · 43 张（普 11 / 罕 19 / 稀 13 · §5.1–5.3）</t>
+          <t>常规卡池 · 80 张（普 20 / 罕 35 / 稀 25 · §5.1–5.3）</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2724,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -4660,7 +4661,7 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>v1.2 替换记录：三连骰→洗劫、出老千→叠注、催债人→连胜、铁赌桌→当铺、脚底抹油→高利贷、切牌→数牌、金库→买凶、威逼利诱→黑吃黑、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
+          <t>v1.2 替换记录（旧名→当前名）：三连骰→清台、出老千→叠注、催债人→连胜、铁赌桌→兑筹、脚底抹油→高利贷、切牌→数牌、金库→打庄、威逼利诱→抽佣、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
         </is>
       </c>
     </row>
@@ -4685,14 +4686,11 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
   </sheetData>
   <autoFilter ref="B4:J49"/>
   <mergeCells count="7">
+    <mergeCell ref="B87:J87"/>
     <mergeCell ref="B90:J90"/>
-    <mergeCell ref="B87:J87"/>
     <mergeCell ref="B89:J89"/>
     <mergeCell ref="B88:J88"/>
     <mergeCell ref="B2:J2"/>
@@ -4709,7 +4707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4797,7 +4795,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>赌一把</t>
+          <t>买定离手</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -4829,7 +4827,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>灵光一闪</t>
+          <t>盲注</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -4925,7 +4923,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>雇佣打手</t>
+          <t>摇骰</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -5181,7 +5179,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>天命</t>
+          <t>单双</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -5210,41 +5208,172 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>反水</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>5 挡</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>9 挡+9 伤</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>12.9（挡×1.2 折伤）</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>10.2 伤（1能+2金@2.1）</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+    </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>连庄</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>8 挡 ×3 次</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>12 挡（14.4 伤当量）</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>12 伤（2 能）</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>押宝</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>18 伤+自伤 6</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>25 伤</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>≈20</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>16.5 伤（1能+5金@2.1）</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>押牌</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>8 伤+弃 2 手牌</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>15 伤</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>≈9.4（弃牌折价）</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>6 伤（打击）</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>≈1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="B23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>白板基准取自池内同费非赌博卡与基础牌（打击 6 伤 / 防御 5 挡 / 双费按 §2.1 补贴率折算，AoE 按单体 × 0.7）。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="B21" s="7" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>* 双倍下注因"双倍"叙事锁定 2× 结构，取整后为 1.25；连胜期望已含连锁上限截断，做局（必正/全正）下每一连锁点均进一步放大期望。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>† 天命基准 = 1 能费用牌的公允净收益 ≈ +0.4 能量；纯方差彩蛋单列，做局下收益急剧放大（赌神 = 无条件净 +3 能量）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>折算口径：自伤按 0.5:1 折价计入期望；抽牌按 2 金/张折入金当量；真赌牌因反面带惩罚，强档倍率可偏离 2×，以期望 1.2× 为准。</t>
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>† 单双基准 = 1 能费用牌的公允净收益 ≈ +0.4 能量；纯方差彩蛋单列，做局下收益急剧放大（赌神 = 无条件净 +3 能量）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>折算口径：自伤按 0.5:1 折价计入期望；抽牌按 2 金/张折入金当量；格挡按 1.2:1 折成伤当量（基线 5 挡 vs 6 伤）；真赌牌因反面带惩罚，强档倍率可偏离 2×，以期望 1.2× 为准。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B25:G25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5256,7 +5385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5508,7 +5637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5628,7 +5757,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>17：双费 16（普5/罕5/稀6）＋可变投入·加注</t>
+          <t>34：固定 30（普 8/罕 10/稀 12）＋ X 倍 2（梭哈/全下）＋ 可变投入 2（加注/再加注）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -5650,7 +5779,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>18（起始1/普3/罕8/稀6）</t>
+          <t>18（起始1/普2/罕9/稀6）</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5672,7 +5801,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>14（v1.7 新增 零钱堆/人头费/抽水/收账）</t>
+          <t>14（本钱/筹码/悬红/清台/派彩/抽头/兑筹/高利贷/爆机/老虎机/散码/买码/抽水/清码）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5694,7 +5823,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3（存钱罐/赌场规则/利滚利）</t>
+          <t>3（返水/台规/利滚利）</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5716,7 +5845,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>5（+孤注/押牌）</t>
+          <t>5（孤注一掷/俄罗斯轮盘/单双/押宝/押牌；罕稀两档）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -5738,7 +5867,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2（老虎机/贪婪重击）</t>
+          <t>2（老虎机/爆机）</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -5760,7 +5889,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>8（+蓄风/加倍/出千）</t>
+          <t>8（遗物/暗记/手气正旺/赌神/叠码/倍投/出千/底牌-条件）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -5782,7 +5911,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10 挂词条（9 + 兑筹码）＋ 2 只读条件（叠注/底牌）</t>
+          <t>10 挂词条（9 + 换筹）＋ 2 只读条件（叠注/底牌）</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5805,7 +5934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6011,6 +6140,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="34" customHeight="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -6033,7 +6163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6042,6 +6172,7 @@
     <col width="42" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -6049,6 +6180,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -6130,7 +6262,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>动它牵动全部 14 张赌博牌，逐卡见 §5.4</t>
+          <t>动它牵动全部 18 张赌博牌，逐卡见 §5.4</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6313,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>动它平移全部 11 张倍率关联牌；倍率不设上限（含金币）已定，经济风险已接受（§2.8）</t>
+          <t>动它平移全部 12 张倍率关联牌；倍率不设上限（含金币）已定，经济风险已接受（§2.8）</t>
         </is>
       </c>
     </row>

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="B2:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -633,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="B2:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -750,7 +750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="B2:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="34" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -972,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A2:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -991,7 +990,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>常规卡池 · 80 张（普 20 / 罕 35 / 稀 25 · §5.1–5.3）</t>
+          <t>常规卡池 · 76 张（普 20 / 罕 33 / 稀 23 · §5.1–5.3）</t>
         </is>
       </c>
     </row>
@@ -1809,683 +1808,683 @@
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="B22" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>连胜★</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>摇骰</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>1能+5金</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>赌博·随机多段</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>对随机敌人造成 4 伤害 3 次。赌博：正面 → 每次 9</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>5×3 / 正面每次 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="38" customHeight="1">
+      <c r="B23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>暗记</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>做局·下一掷必正</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>你的下一次赌博必为正面</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>接下来 2 次必为正面</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>派彩</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>2能+3金</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>投资回本</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>获得 18 金币，抽 1 张牌</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>获得 22 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>数牌★</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>算牌·信息优势</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>查看抽牌堆顶 3 张，可将其中任意张置入弃牌堆</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>顶 4 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="B26" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>兑筹★</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>牌换金·卡组精简</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>消耗手牌 1 张，获得 12 金币</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>获得 16 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1">
+      <c r="B27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>抽头</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>赌博·连锁（上限2）</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>造成 5 伤害。赌博：正面 → 再次触发本效果并再次赌博（最多连锁 2 次）</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>基础 7 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="38" customHeight="1">
-      <c r="B23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>赌博·产金</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>获得 7 金币。赌博：正面 → 改为 14 金币</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>9 / 正面 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="B28" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>摇骰</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>1能+2金</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>反向赌博（盼反面）</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>获得 8 格挡。赌博：反面 → 改为 16 格挡</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>10 / 反面 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="B29" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>假筹</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>金币费用豁免</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>你的下一次金币花费不消耗金币</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>本场战斗前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>高利贷★</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>跨战斗贷款</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>获得 18 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="B31" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>手气正旺</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>做局·被动概率</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>赌博正面率 +15%</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>台规</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>收入×正面联动</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>每回合开始获得 4 金币；每次掷出正面，额外获得 3 金币</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>每回合 5 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="38" customHeight="1">
+      <c r="B33" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>流水</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>花费追踪·转抽牌</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>你每累计花费 10 金币，抽 1 张牌</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>每累计 8 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>孤注一掷</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>1能+5金</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>赌博·随机多段</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>对随机敌人造成 4 伤害 3 次。赌博：正面 → 每次 9</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>5×3 / 正面每次 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>暗记</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>1能+10金</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>✔真赌</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>真赌·尖刺</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>造成 27 伤害。赌博：正面 → 改为 43 伤害；反面 → 改为 25 伤害且自己受到 6 伤害</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>正面 50 / 反面 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="B35" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>俄罗斯轮盘</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>✔真赌</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>真赌·自伤多段</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>对随机敌人造成 3 伤害 5 次。赌博：正面 → 每次改为 5；反面 → 其中 2 发改为打自己（自己共受 10 伤害）</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>每次 4 / 正面 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1">
+      <c r="B36" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>爆机</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>3能+8金</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>做局·下一掷必正</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>你的下一次赌博必为正面</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>接下来 2 次必为正面</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>派彩</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>2能+3金</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>投资回本</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>获得 18 金币，抽 1 张牌</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>获得 22 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="38" customHeight="1">
-      <c r="B26" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>数牌★</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>算牌·信息优势</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>查看抽牌堆顶 3 张，可将其中任意张置入弃牌堆</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>顶 4 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="38" customHeight="1">
-      <c r="B27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>兑筹★</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>牌换金·卡组精简</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>消耗手牌 1 张，获得 12 金币</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>获得 16 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="B28" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>抽头</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>赌博·产金</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>获得 7 金币。赌博：正面 → 改为 14 金币</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>9 / 正面 18</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="38" customHeight="1">
-      <c r="B29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>1能+2金</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>反向赌博（盼反面）</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>获得 8 格挡。赌博：反面 → 改为 16 格挡</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>10 / 反面 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>假筹</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>金币费用豁免</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>你的下一次金币花费不消耗金币</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>本场战斗前 2 次</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="38" customHeight="1">
-      <c r="B31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>高利贷★</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>跨战斗贷款</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>获得 18 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>手气正旺</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>做局·被动概率</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>赌博正面率 +15%</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="38" customHeight="1">
-      <c r="B33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>台规</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>收入×正面联动</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>每回合开始获得 4 金币；每次掷出正面，额外获得 3 金币</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>每回合 5 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>流水</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>花费追踪·转抽牌</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>你每累计花费 10 金币，抽 1 张牌</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>每累计 8 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="54" customHeight="1">
-      <c r="B35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>孤注一掷</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>1能+10金</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>✔真赌</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>真赌·尖刺</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>造成 27 伤害。赌博：正面 → 改为 43 伤害；反面 → 改为 25 伤害且自己受到 6 伤害</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>正面 50 / 反面 29</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="54" customHeight="1">
-      <c r="B36" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>俄罗斯轮盘</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>✔真赌</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>真赌·自伤多段</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>对随机敌人造成 3 伤害 5 次。赌博：正面 → 每次改为 5；反面 → 其中 2 发改为打自己（自己共受 10 伤害）</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>每次 4 / 正面 6</t>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>头奖·击杀产金大</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>造成 35 伤害。击杀则获得 25 金币</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>40 伤害</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="B37" s="5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
@@ -2494,7 +2493,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>爆机</t>
+          <t>同花顺</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2504,33 +2503,33 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>3能+8金</t>
+          <t>3能+12金</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>头奖·击杀产金大</t>
+          <t>兑现·终结</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>造成 35 伤害。击杀则获得 25 金币</t>
+          <t>造成 43 伤害 ×倍率</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>40 伤害</t>
+          <t>46 伤害</t>
         </is>
       </c>
     </row>
     <row r="38" ht="38" customHeight="1">
       <c r="B38" s="6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
@@ -2539,808 +2538,808 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>单双</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>✔真赌</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>真赌·能量</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>赌博：正面 → 获得 4 点能量；反面 → 失去 1 点能量</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>正面 5 点能量</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="38" customHeight="1">
+      <c r="B39" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>打庄★</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>2能+10金</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>✔×3</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>赌博·逐击独立</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>造成 9 伤害 3 次，每击独立赌博：正面则该击改为 18</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>每击 10 / 正面 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="38" customHeight="1">
-      <c r="B39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>2能+15金</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>定向斩杀（最低生命）</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>对生命值最低的敌人造成 43 伤害</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>50 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="38" customHeight="1">
+      <c r="B40" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>同花顺</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>3能+12金</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>兑现·终结</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>造成 43 伤害 ×倍率</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>46 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="38" customHeight="1">
-      <c r="B40" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>弃牌</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>自消耗换值</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>抽 2 张牌，获得 14 金币</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>抽 3 张，18 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="38" customHeight="1">
+      <c r="B41" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>单双</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>抽佣★</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>✔真赌</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>真赌·能量</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>赌博：正面 → 获得 4 点能量；反面 → 失去 1 点能量</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>正面 5 点能量</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="38" customHeight="1">
-      <c r="B41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>2能+8金</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>力量剥夺</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>施加 5 点力量削弱与 3 易伤</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>6 点力量削弱与 4 易伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>老虎机</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>底牌</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>2能+5金</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>✔×3</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>头奖·多次掷产金引擎</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>赌博 3 次，每次正面：获得 9 金币并抽 1 张牌</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>每次正面 11 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>倍率条件·抽牌</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>抽 2 张牌。若倍率 ≥1.5，额外抽 1 张牌</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>抽 3 张牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>打庄★</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>2能+15金</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>赌神</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>3能</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>定向斩杀（最低生命）</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>对生命值最低的敌人造成 43 伤害</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>50 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>做局·终极全正</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>你的所有赌博视为正面</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>费用变为 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="38" customHeight="1">
+      <c r="B44" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>弃牌</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>利滚利★</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>消耗</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>自消耗换值</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>抽 2 张牌，获得 14 金币</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>抽 3 张，18 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="38" customHeight="1">
-      <c r="B44" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>抽佣★</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>2能+8金</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>力量剥夺</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>施加 5 点力量削弱与 3 易伤</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>6 点力量削弱与 4 易伤</t>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>产金放大器</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>本场战斗中你每次获得金币时，额外获得 2 金币</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>额外 3 金币</t>
         </is>
       </c>
     </row>
     <row r="45" ht="38" customHeight="1">
       <c r="B45" s="5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>收手</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>兑现·格挡</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>获得 5 格挡 ×倍率</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>8 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>乘胜</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>兑现·单体</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>造成 6 伤害 ×倍率</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>9 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="B47" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>割禾青</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>倍率折算·抽牌</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>每 0.5 倍率抽 1 张牌（至多 3 张）</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>至多 4 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>兑现</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>兑现·产金</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>获得 7 金币 ×倍率</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>通杀</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>2能+5金</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>兑现·AoE</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>对所有敌人造成 16 伤害 ×倍率</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>20 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>底牌</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>晒冷</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>3能+15金</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>兑现·大炮</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>造成 50 伤害 ×倍率</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>62 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>追数</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>2能+8金</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>兑现·击杀续风</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>造成 29 伤害 ×倍率；若击杀则本次不清空倍率</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>36 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="B52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>割肉</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>倍率条件·抽牌</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>抽 2 张牌。若倍率 ≥1.5，额外抽 1 张牌</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>抽 3 张牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>赌神</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>3能</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>做局·终极全正</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>你的所有赌博视为正面</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>费用变为 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="38" customHeight="1">
-      <c r="B47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>利滚利★</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>产金放大器</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>额外 3 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>收手</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>兑现·格挡</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>获得 5 格挡 ×倍率</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>8 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>乘胜</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>兑现·单体</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>造成 6 伤害 ×倍率</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>9 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>割禾青</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>倍率折算·抽牌</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>每 0.5 倍率抽 1 张牌（至多 3 张）</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>至多 4 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="B51" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>兑现</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>兑现·产金</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>获得 7 金币 ×倍率</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>获得 9 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>通杀</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>2能+5金</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>兑现·AoE</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>对所有敌人造成 16 伤害 ×倍率</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>20 伤害</t>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>兑现·自伤</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>获得 10 格挡 ×倍率；自身失去「倍率 ×3」生命</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>13 格挡</t>
         </is>
       </c>
     </row>
     <row r="53" ht="54" customHeight="1">
       <c r="B53" s="5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>晒冷</t>
+          <t>散码</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>3能+15金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>兑现·大炮</t>
+          <t>即时产金·弃牌堆</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>造成 50 伤害 ×倍率</t>
+          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8）</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>62 伤害</t>
+          <t>至多 12</t>
         </is>
       </c>
     </row>
     <row r="54" ht="54" customHeight="1">
       <c r="B54" s="5" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>追数</t>
+          <t>买码</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>兑现·击杀续风</t>
+          <t>即时产金·敌人数</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>造成 29 伤害 ×倍率；若击杀则本次不清空倍率</t>
+          <t>每个敌人给予 5 金币</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>36 伤害</t>
+          <t>每敌人 7 金</t>
         </is>
       </c>
     </row>
     <row r="55" ht="54" customHeight="1">
       <c r="B55" s="5" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>割肉</t>
+          <t>吃水</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+4金</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>兑现·自伤</t>
+          <t>击杀产金·溢出转金</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>获得 10 格挡 ×倍率；自身失去「倍率 ×3」生命</t>
+          <t>造成 12 伤害；**溢出的伤害**转为金币</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>13 格挡</t>
+          <t>16 伤害</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="B56" s="5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
@@ -3349,7 +3348,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>散码</t>
+          <t>点码</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -3369,23 +3368,23 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>即时产金·弃牌堆</t>
+          <t>花费追踪·转格挡</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8）</t>
+          <t>获得 5 格挡；本回合每花费过 5 金币，额外 +3 格挡</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>每 5 金 +4</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="B57" s="5" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
@@ -3394,7 +3393,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>买码</t>
+          <t>洗牌</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3414,23 +3413,23 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>即时产金·敌人数</t>
+          <t>弃牌换抽</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>每个敌人给予 5 金币</t>
+          <t>弃置 1 张手牌，抽 2 张牌</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>每敌人 7 金</t>
+          <t>抽 3 张</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="B58" s="5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
@@ -3439,12 +3438,12 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>吃水</t>
+          <t>护池</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -3459,23 +3458,23 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>击杀产金·溢出转金</t>
+          <t>附加费·多段格挡</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>造成 12 伤害；**溢出的伤害**转为金币</t>
+          <t>获得 5 格挡 3 次</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>16 伤害</t>
+          <t>7 格挡 3 次</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="B59" s="5" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
@@ -3484,7 +3483,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>点码</t>
+          <t>换码</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3494,168 +3493,168 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
+          <t>0能+6金</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>附加费·买能量</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>获得 2 点能量</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>获得 3 点</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>再加注</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>花费追踪·转格挡</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>获得 5 格挡；本回合每花费过 5 金币，额外 +3 格挡</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>每 5 金 +4</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="B60" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>洗牌</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>可变投入·档位解锁</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>自动花费至多 9 金：造成 8 伤害；≥3 金另施加 2 易伤；≥6 金另抽 1 张；≥9 金再 +8 伤害</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>抽水</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>弃牌换抽</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>弃置 1 张手牌，抽 2 张牌</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>抽 3 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="B61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>护池</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>1能+4金</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>附加费·多段格挡</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>获得 5 格挡 3 次</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>7 格挡 3 次</t>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>即时产金·手牌数</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>每张手牌获得 1 金币（至多 8）</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>至多 12</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
-      <c r="B62" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>换码</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>0能+6金</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>附加费·买能量</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>获得 2 点能量</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>获得 3 点</t>
+      <c r="B62" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>押宝</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>1能+5金</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>✔真赌</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>真赌·押 HP</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>造成 18 伤害。赌博：正面 → 25 伤害；反面 → 自己失去 6 点生命</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>24 / 31</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="B63" s="6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
@@ -3664,43 +3663,43 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>再加注</t>
+          <t>反水</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>可变投入·档位解锁</t>
+          <t>赌博·格挡反击</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>自动花费至多 9 金：造成 8 伤害；≥3 金另施加 2 易伤；≥6 金另抽 1 张；≥9 金再 +8 伤害</t>
+          <t>赌博：正面 → 获得 9 格挡并造成 9 伤害；反面 → 获得 5 格挡</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>12 伤害</t>
+          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="B64" s="6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
@@ -3709,7 +3708,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>叠码</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -3729,23 +3728,23 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>即时产金·手牌数</t>
+          <t>做局·倍率注入</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>每张手牌获得 1 金币（至多 8）</t>
+          <t>倍率 +1.0</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>倍率 +1.5</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="B65" s="6" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
@@ -3754,43 +3753,43 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>押宝</t>
+          <t>保底</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>✔真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>真赌·押 HP</t>
+          <t>消耗堆协同·格挡</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>造成 18 伤害。赌博：正面 → 25 伤害；反面 → 自己失去 6 点生命</t>
+          <t>获得 10 格挡；每张**已消耗**的牌 +2 格挡（至多 +10）</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>24 / 31</t>
+          <t>12 格挡</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="B66" s="6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
@@ -3799,7 +3798,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>反水</t>
+          <t>加码</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -3809,33 +3808,33 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>赌博·格挡反击</t>
+          <t>花费追踪·转能量</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>赌博：正面 → 获得 9 格挡并造成 9 伤害；反面 → 获得 5 格挡</t>
+          <t>获得 1 点能量；本回合每花费过 10 金，额外 +1（至多 3）</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>11 / 6</t>
+          <t>每 8 金</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="B67" s="6" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
@@ -3844,7 +3843,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>叠码</t>
+          <t>清码</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3864,23 +3863,23 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>做局·倍率注入</t>
+          <t>手牌换金</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>倍率 +1.0</t>
+          <t>弃置全部手牌，每弃 1 张获得 4 金币</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>倍率 +1.5</t>
+          <t>每张 5 金</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="B68" s="6" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
@@ -3889,17 +3888,17 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>翻盘</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -3909,23 +3908,23 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>消耗堆协同·格挡</t>
+          <t>生命条件</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>获得 10 格挡；每张**已消耗**的牌 +2 格挡（至多 +10）</t>
+          <t>造成 10 伤害；若你的生命低于 50%，改为 24 伤害</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>12 格挡</t>
+          <t>14 / 30</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="B69" s="6" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
@@ -3934,17 +3933,17 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>加码</t>
+          <t>暗注</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3954,23 +3953,23 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>花费追踪·转能量</t>
+          <t>附加费·穿透</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>获得 1 点能量；本回合每花费过 10 金，额外 +1（至多 3）</t>
+          <t>造成 6 点**无视格挡**的伤害</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>每 8 金</t>
+          <t>9 点</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="B70" s="6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
@@ -3979,7 +3978,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>抵押</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -3989,7 +3988,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -3999,23 +3998,23 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>手牌换金</t>
+          <t>特异·卖血换甲</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币</t>
+          <t>获得 12 格挡；自己失去 4 点生命</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>每张 5 金</t>
+          <t>16 格挡</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="B71" s="6" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
@@ -4024,223 +4023,223 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>翻盘</t>
+          <t>换牌</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>特异·消耗换抽</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>消耗 1 张手牌，抽 2 张牌</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>抽 3 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="B72" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>全下</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>1能+3金</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>X能+7X金</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>生命条件</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>造成 10 伤害；若你的生命低于 50%，改为 24 伤害</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>14 / 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="B72" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>暗注</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>1能+6金</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>附加费·X费多段</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>对随机敌人造成 9×X 伤害，共 X 次</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>金币费降为 5×X</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="B73" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>出千</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>附加费·穿透</t>
-        </is>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>造成 6 点**无视格挡**的伤害</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>9 点</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="B73" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>连庄</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>做局·本回合全正</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>本回合你接下来的所有赌博必为正面</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>费用变为 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="B74" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>摊牌</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>✔×3</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>赌博·累积多掷</t>
-        </is>
-      </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>掷硬币 3 次，每次正面获得 8 格挡</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>每次 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="B74" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>抵押</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>特异·弃牌堆规模</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>对随机敌人造成「弃牌堆张数」伤害（至多 20）</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>至多 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="B75" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>保本</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>2能+10金</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>特异·卖血换甲</t>
-        </is>
-      </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>获得 12 格挡；自己失去 4 点生命</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>16 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="B75" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>换牌</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>特异·消耗换抽</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>消耗 1 张手牌，抽 2 张牌</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>抽 3 张</t>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>特异·金币转格挡</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>消耗你一半金币，获得等量格挡（至多 30）</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>至多 40</t>
         </is>
       </c>
     </row>
     <row r="76" ht="54" customHeight="1">
       <c r="B76" s="5" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
@@ -4249,7 +4248,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>全下</t>
+          <t>押牌</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -4259,33 +4258,33 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>X能+7X金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔真赌</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>附加费·X费多段</t>
+          <t>真赌·押手牌</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>对随机敌人造成 9×X 伤害，共 X 次</t>
+          <t>造成 8 伤害。赌博：正面 → 15 伤害；反面 → 弃掉 2 张手牌</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>金币费降为 5×X</t>
+          <t>12 / 19</t>
         </is>
       </c>
     </row>
     <row r="77" ht="54" customHeight="1">
       <c r="B77" s="5" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
@@ -4294,17 +4293,17 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>出千</t>
+          <t>截胡</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>2能+8金</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -4314,23 +4313,23 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>做局·本回合全正</t>
+          <t>击杀产金·处决</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>本回合你接下来的所有赌博必为正面</t>
+          <t>对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>26 伤害</t>
         </is>
       </c>
     </row>
     <row r="78" ht="54" customHeight="1">
       <c r="B78" s="5" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
@@ -4339,7 +4338,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>摊牌</t>
+          <t>倍投</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -4359,23 +4358,23 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>特异·弃牌堆规模</t>
+          <t>做局·倍率翻倍</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>对随机敌人造成「弃牌堆张数」伤害（至多 20）</t>
+          <t>你的倍率**翻倍**</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>至多 28</t>
+          <t>费用变为 1</t>
         </is>
       </c>
     </row>
     <row r="79" ht="54" customHeight="1">
       <c r="B79" s="5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
@@ -4384,7 +4383,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>保本</t>
+          <t>换筹</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -4394,33 +4393,33 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>特异·金币转格挡</t>
+          <t>风头·兑现能量</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>消耗你一半金币，获得等量格挡（至多 30）</t>
+          <t>按倍率折算能量：获得「倍率取整」点能量，结算后清空</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>至多 40</t>
+          <t>+1 点</t>
         </is>
       </c>
     </row>
     <row r="80" ht="54" customHeight="1">
       <c r="B80" s="5" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
@@ -4429,7 +4428,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>押牌</t>
+          <t>满贯</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -4439,248 +4438,68 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+18金</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>✔真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>真赌·押手牌</t>
+          <t>特异·赌博计数</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>造成 8 伤害。赌博：正面 → 15 伤害；反面 → 弃掉 2 张手牌</t>
+          <t>造成 30 伤害；若本场战斗中你掷出过正面，改为 50 伤害</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>12 / 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="54" customHeight="1">
-      <c r="B81" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>截胡</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>2能+8金</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>击杀产金·处决</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>26 伤害</t>
-        </is>
-      </c>
-    </row>
+          <t>38 / 62</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="54" customHeight="1"/>
     <row r="82" ht="54" customHeight="1">
-      <c r="B82" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>倍投</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>做局·倍率翻倍</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>你的倍率**翻倍**</t>
-        </is>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>费用变为 1</t>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>费用列简写："1能+5金" = 1 能量 + 5 金币；赌博列"✔"表示带赌博词条（"风头"= 带「风头正盛」词条，v1.6 新增），真赌标注反面惩罚；★ = v1.2 新钩子卡；效果列均已按当前代码实装校对。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="54" customHeight="1">
-      <c r="B83" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>换筹</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>风头·兑现能量</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>按倍率折算能量：获得「倍率取整」点能量，结算后清空</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>+1 点</t>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>v1.2 重设计原则：一张卡 = 一个钩子。消灭纯数值变体，每张卡在"钩子"列声明其独有机制，同家族不重复占位。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="54" customHeight="1">
-      <c r="B84" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>满贯</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>2能+18金</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>特异·赌博计数</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>造成 30 伤害；若本场战斗中你掷出过正面，改为 50 伤害</t>
-        </is>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>38 / 62</t>
-        </is>
-      </c>
-    </row>
-    <row r="85"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>v1.2 替换记录（旧名→当前名）：三连骰→清台、出老千→叠注、催债人→连胜、铁赌桌→兑筹、脚底抹油→高利贷、切牌→数牌、金库→打庄、威逼利诱→抽佣、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>v1.3 评审删除：「换骰」「操纵牌局」——不做重掷机制，删后不补新卡（卡池 45→43，编号已重排，见设计文档 §5）。</t>
+        </is>
+      </c>
+    </row>
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>费用列简写："1能+5金" = 1 能量 + 5 金币；赌博列"✔"表示带赌博词条（"风头"= 带「风头正盛」词条，v1.6 新增），真赌标注反面惩罚；★ = v1.2 新钩子卡；效果列均已按当前代码实装校对。</t>
+          <t>实装同步注记（以代码为准）：加注为自动花费至多 6 金币（选额 UI 留美术资产批）；数牌为选 1 张置入弃牌堆；底牌正面改为额外抽 1 张（原设计"费用 -1"待费用修改器接入后还原）。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
-        <is>
-          <t>v1.2 重设计原则：一张卡 = 一个钩子。消灭纯数值变体，每张卡在"钩子"列声明其独有机制，同家族不重复占位。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>v1.2 替换记录（旧名→当前名）：三连骰→清台、出老千→叠注、催债人→连胜、铁赌桌→兑筹、脚底抹油→高利贷、切牌→数牌、金库→打庄、威逼利诱→抽佣、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>v1.3 评审删除：「换骰」「操纵牌局」——不做重掷机制，删后不补新卡（卡池 45→43，编号已重排，见设计文档 §5）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>实装同步注记（以代码为准）：加注为自动花费至多 6 金币（选额 UI 留美术资产批）；数牌为选 1 张置入弃牌堆；底牌正面改为额外抽 1 张（原设计"费用 -1"待费用修改器接入后还原）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
         <is>
           <t>注：「保险」是反向赌博（反面才强化），全池唯一一张"盼反面"的普通赌博牌，为真赌牌和做局留心理准备。</t>
         </is>
@@ -4707,7 +4526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5017,157 +4836,157 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>连胜</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>5 伤</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>5×2（连锁）</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>8.75</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>7 伤（1 能）</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>1.25*</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>孤注一掷</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>25 伤+自伤 6</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>43 伤</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>≈32.5</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>27 伤（1能+10金@2.1）</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>≈1.2</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>豹子</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>9/击</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>18/击</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>40.5</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>33 伤（2能+10金@2.1）</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>1.23</t>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>俄罗斯轮盘</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>3×3 敌+自伤 10</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>5×5</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>12 伤（2 能）</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>1.21</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>老虎机</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>9 金+抽 1/掷</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>≈15 金当量</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>≈11.5 金当量</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>≈1.3</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>单双</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>−1 能</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>+4 能</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>净 +0.5 能</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>单列†</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>≈1.2</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>孤注一掷</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>25 伤+自伤 6</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>43 伤</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>≈32.5</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>27 伤（1能+10金@2.1）</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>≈1.2</t>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>反水</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>5 挡</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>9 挡+9 伤</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>12.9（挡×1.2 折伤）</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>10.2 伤（1能+2金@2.1）</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>1.26</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>俄罗斯轮盘</t>
+          <t>押宝</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>3×3 敌+自伤 10</t>
+          <t>18 伤+自伤 6</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5×5</t>
+          <t>25 伤</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>≈20</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>12 伤（2 能）</t>
+          <t>16.5 伤（1能+5金@2.1）</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -5179,27 +4998,27 @@
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>单双</t>
+          <t>押牌</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>−1 能</t>
+          <t>8 伤+弃 2 手牌</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+4 能</t>
+          <t>15 伤</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>净 +0.5 能</t>
+          <t>≈9.4（弃牌折价）</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>单列†</t>
+          <t>6 伤（打击）</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -5209,159 +5028,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>反水</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>5 挡</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>9 挡+9 伤</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>12.9（挡×1.2 折伤）</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>10.2 伤（1能+2金@2.1）</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
+      <c r="B19" s="7" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>连庄</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>8 挡 ×3 次</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>12 挡（14.4 伤当量）</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>12 伤（2 能）</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>1.20</t>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>白板基准取自池内同费非赌博卡与基础牌（打击 6 伤 / 防御 5 挡 / 双费按 §2.1 补贴率折算，AoE 按单体 × 0.7）。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>押宝</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>18 伤+自伤 6</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>25 伤</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>≈20</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>16.5 伤（1能+5金@2.1）</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>1.21</t>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>* 双倍下注因"双倍"叙事锁定 2× 结构，取整后为 1.25。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>押牌</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>8 伤+弃 2 手牌</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>15 伤</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>≈9.4（弃牌折价）</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>6 伤（打击）</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>≈1.2</t>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>† 单双基准 = 1 能费用牌的公允净收益 ≈ +0.4 能量；纯方差彩蛋单列，做局下收益急剧放大（赌神 = 无条件净 +3 能量）。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="B23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>白板基准取自池内同费非赌博卡与基础牌（打击 6 伤 / 防御 5 挡 / 双费按 §2.1 补贴率折算，AoE 按单体 × 0.7）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>* 双倍下注因"双倍"叙事锁定 2× 结构，取整后为 1.25；连胜期望已含连锁上限截断，做局（必正/全正）下每一连锁点均进一步放大期望。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>† 单双基准 = 1 能费用牌的公允净收益 ≈ +0.4 能量；纯方差彩蛋单列，做局下收益急剧放大（赌神 = 无条件净 +3 能量）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>折算口径：自伤按 0.5:1 折价计入期望；抽牌按 2 金/张折入金当量；格挡按 1.2:1 折成伤当量（基线 5 挡 vs 6 伤）；真赌牌因反面带惩罚，强档倍率可偏离 2×，以期望 1.2× 为准。</t>
         </is>
@@ -5385,7 +5076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="B2:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5484,7 +5175,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>按生命值、按回合数</t>
+          <t>按生命值、按回合数、多次掷产金（老虎机，v1.8 腾空）</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5221,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>基础（试手气）/ AoE（买定离手）/ 格挡（盲注）/ 双段（双倍下注）/ 尖刺（翻本）/ 连锁（连胜）/ 逐击（豹子）/ 随机多段（摇骰）/ 反向（保险）/ 累积多掷（连庄）/ 格挡反击（反水）</t>
+          <t>基础（试手气）/ AoE（买定离手）/ 格挡（盲注）/ 双段（双倍下注）/ 尖刺（翻本）/ 随机多段（摇骰）/ 反向（保险）/ 格挡反击（反水）</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>赌博·反伤护体、赌博·复制手牌</t>
+          <t>赌博·反伤护体、赌博·复制手牌、多掷/连锁/逐击（v1.8 随豹子/老虎机/连庄/连胜删除而腾空）</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="B2:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5686,17 +5377,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>80（v1.8 起不再追平）</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>80（v1.3 删 2 后 43；v1.6 +8 到 51；v1.7 +29 补齐模板）</t>
+          <t>76（v1.3 删 2 → 43；v1.6 +8 → 51；v1.7 +29 → 80；v1.8 删 4 张自掷牌 → 76）</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5708,17 +5399,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>20 普 / 35 罕 / 25 稀</t>
+          <t>20 普 / 35 罕 / 25 稀（v1.8 起不再追平）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>20 / 35 / 25（对齐原版模板）</t>
+          <t>20 / 33 / 23（删 2 罕 + 2 稀）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5426,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>32 攻 / 42 技 / 6 能（v1.7 防御向：4 张攻击牌转格挡，格挡牌 9→13）</t>
+          <t>30 攻 / 40 技 / 6 能（v1.7 把护池/保底/抵押/保本 4 张攻击牌转为格挡技能；v1.8 删 2 攻 + 2 技）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5757,7 +5448,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>34：固定 30（普 8/罕 10/稀 12）＋ X 倍 2（梭哈/全下）＋ 可变投入 2（加注/再加注）</t>
+          <t>32：固定 28（普 8/罕 10/稀 10）＋ X 倍 2（梭哈/全下）＋ 可变投入 2（加注/再加注）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -5779,12 +5470,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>18（起始1/普2/罕9/稀6）</t>
+          <t>14（起始 1/普 2/罕 7/稀 4；v1.8 删 豹子/老虎机/连庄/连胜 四张自掷牌）</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>≈</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5492,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>14（本钱/筹码/悬红/清台/派彩/抽头/兑筹/高利贷/爆机/老虎机/散码/买码/抽水/清码）</t>
+          <t>13（本钱/筹码/悬红/清台/派彩/抽头/兑筹/高利贷/爆机/散码/买码/抽水/清码）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5867,7 +5558,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2（老虎机/爆机）</t>
+          <t>1（爆机）</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -5934,7 +5625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="B2:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6140,7 +5831,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="34" customHeight="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -6163,7 +5853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="B2:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6172,7 +5862,6 @@
     <col width="42" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -6180,7 +5869,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J87"/>
+  <dimension ref="B2:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -990,7 +990,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>常规卡池 · 76 张（普 20 / 罕 33 / 稀 23 · §5.1–5.3）</t>
+          <t>常规卡池 · 85 张（普 24 / 罕 35 / 稀 26 · §5.1–5.3）</t>
         </is>
       </c>
     </row>
@@ -4462,44 +4462,289 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="54" customHeight="1"/>
+    <row r="81" ht="54" customHeight="1">
+      <c r="B81" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>封口</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>出千·必正生成</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>获得 1 次必正，抽 1 张牌</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>获得 2 次必正</t>
+        </is>
+      </c>
+    </row>
     <row r="82" ht="54" customHeight="1">
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>偷天换日</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>出千·赌博转必正</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>造成 5 伤害。赌博：正面 → 额外获得 1 次必正</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>造成 8 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="54" customHeight="1">
+      <c r="B83" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>血本</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>赌命·自伤换能量</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>失去 5 点生命，获得 2 点能量</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>失去 4 点生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="54" customHeight="1">
+      <c r="B84" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>放血</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>赌命·自伤输出</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>造成 9 伤害，自己失去 3 点生命</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>造成 12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>收网</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>出千·必正兑现</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>消耗所有必正，每 1 次造成 9 伤害</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>每次 12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="5" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="5" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="5" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="5" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91">
+      <c r="B91" t="inlineStr">
         <is>
           <t>费用列简写："1能+5金" = 1 能量 + 5 金币；赌博列"✔"表示带赌博词条（"风头"= 带「风头正盛」词条，v1.6 新增），真赌标注反面惩罚；★ = v1.2 新钩子卡；效果列均已按当前代码实装校对。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="54" customHeight="1">
-      <c r="B83" t="inlineStr">
+    <row r="92">
+      <c r="B92" t="inlineStr">
         <is>
           <t>v1.2 重设计原则：一张卡 = 一个钩子。消灭纯数值变体，每张卡在"钩子"列声明其独有机制，同家族不重复占位。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="54" customHeight="1">
-      <c r="B84" t="inlineStr">
+    <row r="93">
+      <c r="B93" t="inlineStr">
         <is>
           <t>v1.2 替换记录（旧名→当前名）：三连骰→清台、出老千→叠注、催债人→连胜、铁赌桌→兑筹、脚底抹油→高利贷、切牌→数牌、金库→打庄、威逼利诱→抽佣、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" t="inlineStr">
+    <row r="94">
+      <c r="B94" t="inlineStr">
         <is>
           <t>v1.3 评审删除：「换骰」「操纵牌局」——不做重掷机制，删后不补新卡（卡池 45→43，编号已重排，见设计文档 §5）。</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" t="inlineStr">
+    <row r="95">
+      <c r="B95" t="inlineStr">
         <is>
           <t>实装同步注记（以代码为准）：加注为自动花费至多 6 金币（选额 UI 留美术资产批）；数牌为选 1 张置入弃牌堆；底牌正面改为额外抽 1 张（原设计"费用 -1"待费用修改器接入后还原）。</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" t="inlineStr">
+    <row r="96">
+      <c r="B96" t="inlineStr">
         <is>
           <t>注：「保险」是反向赌博（反面才强化），全池唯一一张"盼反面"的普通赌博牌，为真赌牌和做局留心理准备。</t>
         </is>
@@ -4526,7 +4771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A2:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5028,36 +5273,71 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="7" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>偷天换日</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>5 伤</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>5 伤+1 必正（≈2 伤当量）</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>6 伤（打击）</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>≈1.17</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>白板基准取自池内同费非赌博卡与基础牌（打击 6 伤 / 防御 5 挡 / 双费按 §2.1 补贴率折算，AoE 按单体 × 0.7）。</t>
-        </is>
-      </c>
+      <c r="B20" s="7" t="n"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>* 双倍下注因"双倍"叙事锁定 2× 结构，取整后为 1.25。</t>
+          <t>白板基准取自池内同费非赌博卡与基础牌（打击 6 伤 / 防御 5 挡 / 双费按 §2.1 补贴率折算，AoE 按单体 × 0.7）。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>† 单双基准 = 1 能费用牌的公允净收益 ≈ +0.4 能量；纯方差彩蛋单列，做局下收益急剧放大（赌神 = 无条件净 +3 能量）。</t>
+          <t>* 双倍下注因"双倍"叙事锁定 2× 结构，取整后为 1.25。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>† 单双基准 = 1 能费用牌的公允净收益 ≈ +0.4 能量；纯方差彩蛋单列，做局下收益急剧放大（赌神 = 无条件净 +3 能量）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
           <t>折算口径：自伤按 0.5:1 折价计入期望；抽牌按 2 金/张折入金当量；格挡按 1.2:1 折成伤当量（基线 5 挡 vs 6 伤）；真赌牌因反面带惩罚，强档倍率可偏离 2×，以期望 1.2× 为准。</t>
         </is>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B24:G24"/>
@@ -5382,7 +5662,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>76（v1.3 删 2 → 43；v1.6 +8 → 51；v1.7 +29 → 80；v1.8 删 4 张自掷牌 → 76）</t>
+          <t>85（v1.3 删 2 → 43；v1.6 +8 → 51；v1.7 +29 → 80；v1.8 删 4 → 76；v1.9 补 9 张四轴牌 → 85）</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5404,7 +5684,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>20 / 33 / 23（删 2 罕 + 2 稀）</t>
+          <t>24 / 35 / 26（v1.9 新卡按 普 4 / 罕 2 / 稀 3 补入）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -5426,7 +5706,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>30 攻 / 40 技 / 6 能（v1.7 把护池/保底/抵押/保本 4 张攻击牌转为格挡技能；v1.8 删 2 攻 + 2 技）</t>
+          <t>34 攻 / 43 技 / 8 能（v1.9 新卡 4 攻 / 3 技 / 2 能）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5448,7 +5728,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>32：固定 28（普 8/罕 10/稀 10）＋ X 倍 2（梭哈/全下）＋ 可变投入 2（加注/再加注）</t>
+          <t>34：固定 30（普 8/罕 10/稀 12）＋ X 倍 2（梭哈/全下）＋ 可变投入 2（加注/再加注）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -5470,7 +5750,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>14（起始 1/普 2/罕 7/稀 4；v1.8 删 豹子/老虎机/连庄/连胜 四张自掷牌）</t>
+          <t>15（起始 1/普 3/罕 7/稀 4；v1.9 新增偷天换日）</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -1078,12 +1078,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>造成 10 伤害</t>
+          <t>造成 11 伤害</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>造成 13 伤害</t>
+          <t>造成 14 伤害</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>加注★</t>
+          <t>加注</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1118,17 +1118,17 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>可变投入·小额</t>
+          <t>花费追踪·每金 +1 伤</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>造成 6 伤害。可额外花费至多 6 金币，每 1 金币 +2 伤害</t>
+          <t>造成 7 伤害。本回合每花费 1 金币，伤害 +1</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>基础 8 伤害</t>
+          <t>基础 10 伤害</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>造成 16 伤害，施加 1 易伤</t>
+          <t>造成 14 伤害，施加 2 易伤</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>19 伤害，2 易伤</t>
+          <t>17 伤害，2 易伤</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>造成 7 伤害。击杀则获得 10 金币</t>
+          <t>造成 9 伤害。击杀则获得 15 金币</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>9 伤害，击杀 +14 金</t>
+          <t>11 伤害，击杀 +19 金</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>获得 4 格挡。赌博：正面 → 改为 8 格挡</t>
+          <t>获得 5 格挡。赌博：正面 → 改为 9 格挡</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>6 / 正面 13</t>
+          <t>7 / 正面 13</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>0能+4金</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
+          <t>抽 2 张牌</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
           <t>抽 3 张牌</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>抽 4 张牌</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
+          <t>施加 3 虚弱</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
           <t>施加 4 虚弱</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>施加 5 虚弱</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>清台★</t>
+          <t>清台</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>叠注★</t>
+          <t>叠注</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>你的下一次赌博必为正面</t>
+          <t>你接下来的 2 次赌博必为正面</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>接下来 2 次必为正面</t>
+          <t>接下来 3 次必为正面</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>数牌★</t>
+          <t>数牌</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>兑筹★</t>
+          <t>兑筹</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>高利贷★</t>
+          <t>高利贷</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>打庄★</t>
+          <t>打庄</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>抽佣★</t>
+          <t>抽佣</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>利滚利★</t>
+          <t>利滚利</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>获得 5 格挡 ×倍率</t>
+          <t>获得 6 格挡 ×倍率</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>8 格挡</t>
+          <t>9 格挡</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>造成 6 伤害 ×倍率</t>
+          <t>造成 7 伤害 ×倍率</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>9 伤害</t>
+          <t>10 伤害</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8）</t>
+          <t>每 2 张弃牌堆的牌，获得 1 金币（不设上限）</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>额外抽 1 张</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>击杀产金·溢出转金</t>
+          <t>即时产金·破盾转金</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>造成 12 伤害；**溢出的伤害**转为金币</t>
+          <t>造成 16 伤害；被格挡抵消的伤害转为金币</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>16 伤害</t>
+          <t>20 伤害</t>
         </is>
       </c>
     </row>
@@ -3373,12 +3373,12 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>获得 5 格挡；本回合每花费过 5 金币，额外 +3 格挡</t>
+          <t>获得 5 格挡；本回合每花费 1 金币，额外 +1 格挡</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>每 5 金 +4</t>
+          <t>基础 8 格挡</t>
         </is>
       </c>
     </row>
@@ -3413,17 +3413,17 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>弃牌换抽</t>
+          <t>牌换金·小额</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>弃置 1 张手牌，抽 2 张牌</t>
+          <t>消耗 1 张手牌，获得 6 金币</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>获得 8 金币</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>0能+5金</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>获得 5 格挡 3 次</t>
+          <t>获得 4 格挡 4 次</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>7 格挡 3 次</t>
+          <t>6 格挡 4 次</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>0能+6金</t>
+          <t>0能+2金</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>获得 2 点能量</t>
+          <t>获得 1 点能量</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>获得 3 点</t>
+          <t>获得 2 点</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>附加费·X费多段</t>
+          <t>可变投入·X费多段</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>获得 1 次必正，抽 1 张牌</t>
+          <t>抽 2 张牌</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>获得 2 次必正</t>
+          <t>获得 2 次必正，抽 2 张牌</t>
         </is>
       </c>
     </row>
@@ -4563,12 +4563,12 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>血本</t>
+          <t>分红</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -4583,17 +4583,17 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>赌命·自伤换能量</t>
+          <t>收入引擎·买血</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>失去 5 点生命，获得 2 点能量</t>
+          <t>每回合开始支付 3 金币，回复 1 点生命（金币不足 3 时不触发）</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>失去 4 点生命</t>
+          <t>回复 2 点生命</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>赌命·自伤输出</t>
+          <t>赌命·自伤产金</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>造成 9 伤害，自己失去 3 点生命</t>
+          <t>失去 2 点生命，获得 20 金币</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>造成 12 伤害</t>
+          <t>获得 26 金币</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G27"/>
+  <dimension ref="B2:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4879,12 +4879,12 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>8（2 能 AoE）</t>
+          <t>4.2（1 能 AoE 折算）</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.26‡</t>
         </is>
       </c>
     </row>
@@ -4896,17 +4896,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>4 挡</t>
+          <t>5 挡</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>8 挡</t>
+          <t>9 挡</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.40‡</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,13 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>‡ v1.10 用户指定加强：买定离手 2 能→1 能、盲注 4/8→5/9，数值未按 1.2× 回锚，期望倍率升到 2.26 / 1.40（有意为之）。</t>
+        </is>
+      </c>
+    </row>
     <row r="26"/>
     <row r="27"/>
   </sheetData>
@@ -5416,7 +5422,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>小额封顶（加注）/ X 费炮（梭哈）/ X 费多段（全下）/ 档位解锁（再加注）</t>
+          <t>X 费炮（梭哈）/ X 费多段（全下）/ 档位解锁（再加注）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -5433,7 +5439,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>单体（悬红）/ AoE（清台）/ 大额头奖（爆机）/ 溢出转金（吃水）/ 处决（截胡）</t>
+          <t>单体（悬红）/ AoE（清台）/ 大额头奖（爆机）/ 处决（截胡）</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -5450,7 +5456,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>基准（筹码）/ 免能量（本钱）/ 投资回本（派彩）/ 掷币（抽头）/ 牌换金（兑筹）/ 贷款（高利贷）/ 弃牌堆（散码）/ 敌人数（买码）/ 手牌数（抽水）/ 手牌换金（清码）</t>
+          <t>基准（筹码）/ 免能量（本钱）/ 投资回本（派彩）/ 掷币（抽头）/ 牌换金（兑筹）/ 贷款（高利贷）/ 弃牌堆（散码）/ 敌人数（买码）/ 手牌数（抽水）/ 手牌换金（清码）/ 破盾转金（吃水）/ 牌换金·小额（洗牌）</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -5467,7 +5473,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>定额（返水）/ 正面触发（台规）/ 增幅（利滚利）</t>
+          <t>定额（返水）/ 正面触发（台规）/ 增幅（利滚利）/ 买血（分红，金→HP）</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -5484,7 +5490,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>转伤害（连续下注）/ 转抽牌（流水）/ 转格挡（点码）/ 转能量（加码）</t>
+          <t>转伤害（连续下注）/ 回响·每金 +1 伤（加注）/ 转抽牌（流水）/ 转格挡（点码）/ 转能量（加码）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -5569,7 +5575,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>费用豁免（假筹）/ 自消耗换值（弃牌）/ 信息（数牌）/ 定向斩杀（打庄）/ 力量剥夺（抽佣）/ 弃牌换抽（洗牌）/ 消耗换抽（换牌）/ 消耗堆协同·格挡（保底）/ 生命条件（翻盘）/ 卖血换甲（抵押）/ 金币转格挡（保本）/ 弃牌堆规模（摊牌）/ 赌博计数（满贯）</t>
+          <t>费用豁免（假筹）/ 自消耗换值（弃牌）/ 信息（数牌）/ 定向斩杀（打庄）/ 力量剥夺（抽佣）/ 消耗换抽（换牌）/ 消耗堆协同·格挡（保底）/ 生命条件（翻盘）/ 卖血换甲（抵押）/ 金币转格挡（保本）/ 弃牌堆规模（摊牌）/ 赌博计数（满贯）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5706,7 +5712,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>34 攻 / 43 技 / 8 能（v1.9 新卡 4 攻 / 3 技 / 2 能）</t>
+          <t>33 攻 / 43 技 / 9 能（v1.10：放血 攻→技；分红 技→能）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5728,7 +5734,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>34：固定 30（普 8/罕 10/稀 12）＋ X 倍 2（梭哈/全下）＋ 可变投入 2（加注/再加注）</t>
+          <t>33：固定 30（普 8/罕 10/稀 12）＋ X 倍 2（梭哈/全下）＋ 可变投入 1（再加注）；另有 1 张花费追踪（加注）不吃基础金费</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -5772,7 +5778,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>13（本钱/筹码/悬红/清台/派彩/抽头/兑筹/高利贷/爆机/散码/买码/抽水/清码）</t>
+          <t>15（本钱/筹码/悬红/清台/派彩/抽头/兑筹/高利贷/爆机/散码/买码/抽水/清码/吃水/洗牌）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -11,11 +11,10 @@
     <sheet name="做局工具" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="起始套牌" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="常规卡池" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="期望校验" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="机制词汇表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="分布统计" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="经济基准" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="平衡旋钮清单" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="机制词汇表" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="分布统计" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="经济基准" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="平衡旋钮清单" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'常规卡池'!$B$4:$J$49</definedName>
@@ -4771,597 +4770,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="10.5" customWidth="1" min="2" max="2"/>
-    <col width="15.1" customWidth="1" min="3" max="3"/>
-    <col width="13.5" customWidth="1" min="4" max="4"/>
-    <col width="13.1" customWidth="1" min="5" max="5"/>
-    <col width="19.6" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1"/>
-    <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>赌博牌期望校验（§5.4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>赌博牌</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>弱档</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>强档</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>期望(50/50)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>白板基准</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>期望倍率</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>试手气</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>5 伤</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>10 伤</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>6 伤（打击）</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>买定离手</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>6（AoE）</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>4.2（1 能 AoE 折算）</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>2.26‡</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>盲注</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>5 挡</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>9 挡</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>5 挡（防御）</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>1.40‡</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>双倍下注</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>10 伤</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>10×2</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>12 伤（2 能）</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>1.25*</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>翻本</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>10 伤</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>20 伤</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>12.3 伤（1能+3金@2.1）</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>摇骰</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>4×3</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>9×3</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>16.5 伤（1能+5金@2.1）</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>抽头</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>7 金</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>14 金</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>10.5 金</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>7 金（1 能产金基准）</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>8 挡（正面）</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>16 挡（反面）</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>10 挡（1能+2金@2.5）</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>孤注一掷</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>25 伤+自伤 6</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>43 伤</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>≈32.5</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>27 伤（1能+10金@2.1）</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>≈1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>俄罗斯轮盘</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>3×3 敌+自伤 10</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>5×5</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>12 伤（2 能）</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>单双</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>−1 能</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>+4 能</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>净 +0.5 能</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>单列†</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>≈1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>反水</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>5 挡</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>9 挡+9 伤</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>12.9（挡×1.2 折伤）</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>10.2 伤（1能+2金@2.1）</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>押宝</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>18 伤+自伤 6</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>25 伤</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>≈20</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>16.5 伤（1能+5金@2.1）</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>押牌</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>8 伤+弃 2 手牌</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>15 伤</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>≈9.4（弃牌折价）</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>6 伤（打击）</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>≈1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>偷天换日</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>5 伤</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>5 伤+1 必正（≈2 伤当量）</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>6 伤（打击）</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>≈1.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="B20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>白板基准取自池内同费非赌博卡与基础牌（打击 6 伤 / 防御 5 挡 / 双费按 §2.1 补贴率折算，AoE 按单体 × 0.7）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>* 双倍下注因"双倍"叙事锁定 2× 结构，取整后为 1.25。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>† 单双基准 = 1 能费用牌的公允净收益 ≈ +0.4 能量；纯方差彩蛋单列，做局下收益急剧放大（赌神 = 无条件净 +3 能量）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>折算口径：自伤按 0.5:1 折价计入期望；抽牌按 2 金/张折入金当量；格挡按 1.2:1 折成伤当量（基线 5 挡 vs 6 伤）；真赌牌因反面带惩罚，强档倍率可偏离 2×，以期望 1.2× 为准。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>‡ v1.10 用户指定加强：买定离手 2 能→1 能、盲注 4/8→5/9，数值未按 1.2× 回锚，期望倍率升到 2.26 / 1.40（有意为之）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B25:G25"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="B2:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5608,7 +5016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5905,7 +5313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6133,13 +5541,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6148,6 +5556,7 @@
     <col width="42" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -6155,6 +5564,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -6224,80 +5634,64 @@
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>赌博期望锚定</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>反面 ≈ 白板 ×0.8 / 正面 ≈ ×1.6，E = 1.2×（0.8+0.8p）</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>动它牵动全部 18 张赌博牌，逐卡见 §5.4</t>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>做局数值上限</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>正面率加法叠加，上限 75%</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>手气正旺 / 赌神的获取难度与数值上限</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>做局数值上限</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>正面率加法叠加，上限 75%</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>手气正旺 / 赌神的获取难度与数值上限</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>梭哈 X 金币系数</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>10×X</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>爆发上限的主要阀门</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>梭哈 X 金币系数</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>10×X</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>爆发上限的主要阀门</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>倍率成长步长 / 风头牌裸值</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+0.5/次正面；裸值按同费常规牌水平</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>动它平移全部 12 张倍率关联牌；倍率不设上限（含金币）已定，经济风险已接受（§2.8）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>倍率成长步长 / 风头牌裸值</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>+0.5/次正面；裸值 = 白板</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>动它平移全部 12 张倍率关联牌；倍率不设上限（含金币）已定，经济风险已接受（§2.8）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>调平衡时动的第一批螺丝，对应设计文档 §7.3；改数值只动卡文件（GamblerMod/src/Cards/），Core 层不动。</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="38" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B12:D12"/>

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>X能+10X金</t>
+          <t>X能+5X金</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>造成 27×X 伤害</t>
+          <t>造成 20×X 伤害</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>金币费降为 8×X</t>
+          <t>金币费降为 4×X</t>
         </is>
       </c>
     </row>
@@ -1612,17 +1612,17 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>花费追踪·转伤害</t>
+          <t>花费追踪·追加伤害</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害</t>
+          <t>造成 9 伤害。本回合若花费过金币，额外造成 1 次伤害</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>额外 +6 伤害</t>
+          <t>额外 2 次</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>击杀产金·AoE收割</t>
+          <t>击杀产金·自我成长</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>对所有敌人造成 13 伤害。每击杀一个敌人，获得 7 金币</t>
+          <t>**消耗**。对所有敌人造成 13 伤害；每击杀一个敌人获得 7 金币；每打出一次，伤害永久 +4</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>造成 8 伤害。若倍率 ≥1.5，改为 16 伤害</t>
+          <t>造成 10 伤害。若倍率 ≥1.5，改为 20 伤害</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>10 / 20</t>
+          <t>12 / 24</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>0能+10金</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>赌博·高方差尖刺</t>
+          <t>赌博·高方差产金</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>造成 10 伤害。赌博：正面 → 改为 20 伤害</t>
+          <t>硬币为正时：获得 25 金币；硬币为负时：获得 5 金币</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>13 / 正面 25</t>
+          <t>6 / 正面 30</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>对随机敌人造成 4 伤害 3 次。赌博：正面 → 每次 9</t>
+          <t>对随机敌人造成 4 伤害 4 次。赌博：正面 → 改为 6 次</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>5×3 / 正面每次 10</t>
+          <t>5×4 / 正面 5×6</t>
         </is>
       </c>
     </row>
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能+3金</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3547,17 +3547,17 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>可变投入·档位解锁</t>
+          <t>附加费·买活力</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>自动花费至多 9 金：造成 8 伤害；≥3 金另施加 2 易伤；≥6 金另抽 1 张；≥9 金再 +8 伤害</t>
+          <t>获得 5 点活力（下次攻击额外造成等量伤害）</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>12 伤害</t>
+          <t>8 点</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>33 攻 / 43 技 / 9 能（v1.10：放血 攻→技；分红 技→能）</t>
+          <t>31 攻 / 45 技 / 9 能（v1.10：放血 攻→技、分红 技→能；v1.12：翻本/再加注 攻→技）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>33：固定 30（普 8/罕 10/稀 12）＋ X 倍 2（梭哈/全下）＋ 可变投入 1（再加注）；另有 1 张花费追踪（加注）不吃基础金费</t>
+          <t>33：固定 31（普 8/罕 10/稀 12 + 再加注）＋ X 倍 2（梭哈/全下）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>15（本钱/筹码/悬红/清台/派彩/抽头/兑筹/高利贷/爆机/散码/买码/抽水/清码/吃水/洗牌）</t>
+          <t>16（本钱/筹码/悬红/清台/派彩/抽头/兑筹/高利贷/爆机/散码/买码/抽水/清码/吃水/洗牌/翻本）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5547,7 +5547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="B2:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5556,7 +5556,6 @@
     <col width="42" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -5564,7 +5563,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2能+3金</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>获得 18 金币，抽 1 张牌</t>
+          <t>获得 18 金币，抽 2 张牌</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>算牌·信息优势</t>
+          <t>即时产金·手牌数</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>查看抽牌堆顶 3 张，可将其中任意张置入弃牌堆</t>
+          <t>每张手牌获得 2 金币</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>顶 4 张</t>
+          <t>每张 3 金币</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>牌换金·卡组精简</t>
+          <t>附加费·买力量</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>消耗手牌 1 张，获得 12 金币</t>
+          <t>获得 2 点力量</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>获得 16 金币</t>
+          <t>获得 3 点力量</t>
         </is>
       </c>
     </row>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>获得 7 金币。赌博：正面 → 改为 14 金币</t>
+          <t>获得 10 金币。赌博：正面 → 改为 20 金币</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>9 / 正面 18</t>
+          <t>12 / 正面 24</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>反向赌博（盼反面）</t>
+          <t>赌博·格挡</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>获得 8 格挡。赌博：反面 → 改为 16 格挡</t>
+          <t>获得 10 格挡。赌博：正面 → 改为 16 格挡</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>10 / 反面 20</t>
+          <t>12 / 正面 19</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -2197,17 +2197,17 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>跨战斗贷款</t>
+          <t>借贷·回合利息</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）</t>
+          <t>获得 50 金币；此后每回合开始失去 5 金币</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>获得 18 金币</t>
+          <t>获得 60 金币</t>
         </is>
       </c>
     </row>
@@ -3592,17 +3592,17 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>即时产金·手牌数</t>
+          <t>出千·必正与活力</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>每张手牌获得 1 金币（至多 8）</t>
+          <t>获得 2 次必正，以及 5 点活力</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>3 次必正</t>
         </is>
       </c>
     </row>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>造成 18 伤害。赌博：正面 → 25 伤害；反面 → 自己失去 6 点生命</t>
+          <t>造成 18 伤害。赌博：正面 → 30 伤害；反面 → 自己失去 3 点生命</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>24 / 31</t>
+          <t>24 / 正面 36 / 反面失 4</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>造成 10 伤害；若你的生命低于 50%，改为 24 伤害</t>
+          <t>造成 6 伤害；若你的生命低于 50%，改为 14 伤害</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>14 / 30</t>
+          <t>8 / 18</t>
         </is>
       </c>
     </row>
@@ -3957,12 +3957,12 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>造成 6 点**无视格挡**的伤害</t>
+          <t>造成 13 点**无视格挡**的伤害</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>9 点</t>
+          <t>16 点</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4672,12 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>出千·必正兑现</t>
+          <t>出千·必正联动</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>消耗所有必正，每 1 次造成 9 伤害</t>
+          <t>你的每 1 次必正造成 9 伤害（不消耗必正）</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>31 攻 / 45 技 / 9 能（v1.10：放血 攻→技、分红 技→能；v1.12：翻本/再加注 攻→技）</t>
+          <t>31 攻 / 44 技 / 10 能（v1.10：放血 攻→技、分红 技→能；v1.12：翻本/再加注 攻→技、高利贷 技→能）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>33：固定 31（普 8/罕 10/稀 12 + 再加注）＋ X 倍 2（梭哈/全下）</t>
+          <t>34：固定 32 ＋ X 倍 2（梭哈/全下）；另有 1 张花费追踪（加注）不吃基础金费</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>16（本钱/筹码/悬红/清台/派彩/抽头/兑筹/高利贷/爆机/散码/买码/抽水/清码/吃水/洗牌/翻本）</t>
+          <t>15（本钱/筹码/悬红/清台/派彩/抽头/高利贷/爆机/散码/买码/清码/吃水/洗牌/翻本/数牌）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -2337,12 +2337,12 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>你每累计花费 10 金币，抽 1 张牌</t>
+          <t>你每累计花费 6 金币，抽 1 张牌</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>每累计 8 金币</t>
+          <t>每累计 5 金币</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -3687,12 +3687,12 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>赌博：正面 → 获得 9 格挡并造成 9 伤害；反面 → 获得 5 格挡</t>
+          <t>硬币为正时：10 格挡 + 10 伤害；硬币为负时：6 格挡 + 6 伤害</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
+          <t>12+12 / 7+7</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>消耗堆协同·格挡</t>
+          <t>消耗堆协同·产金</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>获得 10 格挡；每张**已消耗**的牌 +2 格挡（至多 +10）</t>
+          <t>每张**已消耗**的牌，获得 2 金币</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>12 格挡</t>
+          <t>每张 3 金</t>
         </is>
       </c>
     </row>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>花费追踪·转能量</t>
+          <t>持有量·转能量</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>获得 1 点能量；本回合每花费过 10 金，额外 +1（至多 3）</t>
+          <t>获得 1 点能量；每拥有 50 金币，额外 +1（不设上限）</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>每 8 金</t>
+          <t>基础 2 能量</t>
         </is>
       </c>
     </row>
@@ -3867,12 +3867,12 @@
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币</t>
+          <t>消耗全部手牌，每张获得 7 金币</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>每张 5 金</t>
+          <t>每张 9 金</t>
         </is>
       </c>
     </row>
@@ -3997,17 +3997,17 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>特异·卖血换甲</t>
+          <t>特异·回牌换甲</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>获得 12 格挡；自己失去 4 点生命</t>
+          <t>将 1 张手牌放回抽牌堆，获得 9 格挡</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>16 格挡</t>
+          <t>12 格挡</t>
         </is>
       </c>
     </row>
@@ -4042,17 +4042,17 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>特异·消耗换抽</t>
+          <t>特异·重抽</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>消耗 1 张手牌，抽 2 张牌</t>
+          <t>将任意张手牌放回抽牌堆，再抽等量的牌</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>15（本钱/筹码/悬红/清台/派彩/抽头/高利贷/爆机/散码/买码/清码/吃水/洗牌/翻本/数牌）</t>
+          <t>16（本钱/筹码/悬红/清台/派彩/抽头/高利贷/爆机/散码/买码/清码/吃水/洗牌/翻本/数牌/保底）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -2382,12 +2382,12 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>造成 27 伤害。赌博：正面 → 改为 43 伤害；反面 → 改为 25 伤害且自己受到 6 伤害</t>
+          <t>造成 30 伤害。赌博：正面 → 48 伤害；反面 → 28 伤害且自己受到 6 伤害</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>正面 50 / 反面 29</t>
+          <t>正面 55 / 反面 32</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2417,22 +2417,22 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>✔真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>真赌·自伤多段</t>
+          <t>特异·随机轮盘</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>对随机敌人造成 3 伤害 5 次。赌博：正面 → 每次改为 5；反面 → 其中 2 发改为打自己（自己共受 10 伤害）</t>
+          <t>每回合开始随机开一枪：自己受到 3 伤害并获得 5 金币，或对随机敌人造成 10 伤害</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>每次 4 / 正面 6</t>
+          <t>自己 2 伤+7 金 / 敌人 14 伤</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>3能+8金</t>
+          <t>3能+10金</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>造成 35 伤害。击杀则获得 25 金币</t>
+          <t>造成 40 伤害。击杀则获得 30 金币</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>40 伤害</t>
+          <t>46 伤害</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>3能+12金</t>
+          <t>3能+10金</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>造成 43 伤害 ×倍率</t>
+          <t>造成 48 伤害 ×倍率</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>46 伤害</t>
+          <t>54 伤害</t>
         </is>
       </c>
     </row>
@@ -2552,22 +2552,22 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>✔真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>真赌·能量</t>
+          <t>特异·倍率奇偶</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>赌博：正面 → 获得 4 点能量；反面 → 失去 1 点能量</t>
+          <t>若倍率为偶数：获得 20 金币；若为奇数：获得 2 点力量与 2 点敏捷</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>正面 5 点能量</t>
+          <t>26 金 / 3+3</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2能+15金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>对生命值最低的敌人造成 43 伤害</t>
+          <t>对生命值最低的敌人造成 15 伤害；若你的金币少于 100，伤害翻倍</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>50 伤害</t>
+          <t>19 / 翻倍 38</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>抽 2 张牌，获得 14 金币</t>
+          <t>抽 2 张牌，获得 16 金币</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张，18 金币</t>
+          <t>抽 3 张，20 金币</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能+4金</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>施加 5 点力量削弱与 3 易伤</t>
+          <t>施加 6 点力量削弱与 4 易伤</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>6 点力量削弱与 4 易伤</t>
+          <t>8 点力量削弱与 5 易伤</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>抽 2 张牌。若倍率 ≥1.5，额外抽 1 张牌</t>
+          <t>抽 3 张牌。若倍率 ≥1.5，额外抽 2 张牌</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>抽 3 张牌</t>
+          <t>额外抽 3 张牌</t>
         </is>
       </c>
     </row>
@@ -2832,12 +2832,12 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币</t>
+          <t>本场战斗中你每次获得金币时，额外获得 3 金币</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>额外 3 金币</t>
+          <t>额外 5 金币</t>
         </is>
       </c>
     </row>
@@ -3082,32 +3082,32 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>3能+15金</t>
+          <t>3能</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>兑现·大炮</t>
+          <t>产金转甲</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>造成 50 伤害 ×倍率</t>
+          <t>本场战斗中你每次获得金币时，获得等量格挡</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>62 伤害</t>
+          <t>等量 +5 格挡</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>造成 29 伤害 ×倍率；若击杀则本次不清空倍率</t>
+          <t>造成 20 伤害 ×倍率；若击杀则本次不清空倍率</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>36 伤害</t>
+          <t>24 伤害</t>
         </is>
       </c>
     </row>
@@ -3187,17 +3187,17 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>兑现·自伤</t>
+          <t>兑现·格挡</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>获得 10 格挡 ×倍率；自身失去「倍率 ×3」生命</t>
+          <t>获得 12 格挡 ×倍率</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>13 格挡</t>
+          <t>15 格挡</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>对随机敌人造成 9×X 伤害，共 X 次</t>
+          <t>对随机敌人造成 12×X 伤害，共 X 次</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>对随机敌人造成「弃牌堆张数」伤害（至多 20）</t>
+          <t>对随机敌人造成「弃牌堆张数」伤害（至多 30）</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>至多 28</t>
+          <t>至多 40</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4207,12 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>特异·金币转格挡</t>
+          <t>花费追踪·转敏捷</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>消耗你一半金币，获得等量格挡（至多 30）</t>
+          <t>本场战斗中你每花费 1 金币，获得 1 点敏捷</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>至多 40</t>
+          <t>每金 +1 力量 +1 敏捷</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>真赌·押手牌</t>
+          <t>真赌·退注</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>造成 8 伤害。赌博：正面 → 15 伤害；反面 → 弃掉 2 张手牌</t>
+          <t>获得 2 点能量。赌博：正面 → 返还本次花费的 5 金币</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>12 / 19</t>
+          <t>3 点能量</t>
         </is>
       </c>
     </row>
@@ -4297,12 +4297,12 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -4312,17 +4312,17 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>击杀产金·处决</t>
+          <t>特异·格挡返金</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币</t>
+          <t>获得 16 格挡，并获得等量金币</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>26 伤害</t>
+          <t>20 格挡 / 20 金</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2能+18金</t>
+          <t>1能+9金</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>造成 30 伤害；若本场战斗中你掷出过正面，改为 50 伤害</t>
+          <t>造成 36 伤害；若本场战斗中你掷出过正面，改为 60 伤害</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>38 / 62</t>
+          <t>44 / 72</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>31 攻 / 44 技 / 10 能（v1.10：放血 攻→技、分红 技→能；v1.12：翻本/再加注 攻→技、高利贷 技→能）</t>
+          <t>28 攻 / 44 技 / 13 能（v1.15：轮盘/晒冷 攻→能、截胡 攻→技、保本 技→能）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>34：固定 32 ＋ X 倍 2（梭哈/全下）；另有 1 张花费追踪（加注）不吃基础金费</t>
+          <t>32：固定 30 ＋ X 倍 2（梭哈/全下）；另有 1 张花费追踪（加注）不吃基础金费</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>15（起始 1/普 3/罕 7/稀 4；v1.9 新增偷天换日）</t>
+          <t>13（起始 1/普 3/罕 7/稀 2；v1.15 轮盘与单双去赌博化）</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>16（本钱/筹码/悬红/清台/派彩/抽头/高利贷/爆机/散码/买码/清码/吃水/洗牌/翻本/数牌/保底）</t>
+          <t>17（本钱/筹码/悬红/清台/派彩/抽头/高利贷/爆机/散码/买码/清码/吃水/洗牌/翻本/数牌/保底/截胡）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>5（孤注一掷/俄罗斯轮盘/单双/押宝/押牌；罕稀两档）</t>
+          <t>2（孤注一掷/押宝；v1.15 单双与轮盘去赌博化、押牌改退注后缩减）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10 挂词条（9 + 换筹）＋ 2 只读条件（叠注/底牌）</t>
+          <t>9 挂词条（7 + 同花顺 + 换筹）＋ 2 只读条件（叠注/底牌）</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>赌徒 · 角色总览（§1 · 设计 v1.7）</t>
+          <t>赌徒 · 角色总览（§1 · 设计 v1.15）</t>
         </is>
       </c>
     </row>

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>高于原版（99）：混合费用需要更厚启动本金（设定：本该 150，兑筹抽走两枚「手续费」）</t>
+          <t>高于原版（99）：混合费用需要更厚启动本金（设定：本该 150，重注抽走两枚「手续费」）</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>看场</t>
+          <t>打手</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>盲注</t>
+          <t>跟注</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>兑筹</t>
+          <t>重注</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>假筹</t>
+          <t>假币</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>台规</t>
+          <t>保护费</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>抽佣</t>
+          <t>暗算</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>割禾青</t>
+          <t>见好就收</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>晒冷</t>
+          <t>存钱</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>追数</t>
+          <t>追击</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>割肉</t>
+          <t>止损</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>散码</t>
+          <t>捡漏</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>买码</t>
+          <t>人头费</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>吃水</t>
+          <t>抽税</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>点码</t>
+          <t>记账</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>洗牌</t>
+          <t>典当</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>护池</t>
+          <t>封盘</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>换码</t>
+          <t>充能</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>做手脚</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>反水</t>
+          <t>还手</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>叠码</t>
+          <t>加码</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>回收</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>加码</t>
+          <t>底气</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>清仓</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>抵押</t>
+          <t>留一手</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>押牌</t>
+          <t>押注</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>截胡</t>
+          <t>过路费</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>换筹</t>
+          <t>提现</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>封口</t>
+          <t>发牌</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>伤（底注）/ 格挡（护盘）/ 抽牌（摸牌）/ 纯 debuff（放水）/ 伤+debuff（看场）/ 多段格挡（护池）/ 买能量（换码）/ 穿透（暗注）</t>
+          <t>伤（底注）/ 格挡（护盘）/ 抽牌（摸牌）/ 纯 debuff（放水）/ 伤+debuff（打手）/ 多段格挡（封盘）/ 买能量（充能）/ 穿透（暗注）/ 买活力（再加注）/ 买力量（重注）</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -4830,12 +4830,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>X 费炮（梭哈）/ X 费多段（全下）/ 档位解锁（再加注）</t>
+          <t>X 费炮（梭哈）/ X 费多段（全下）</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>按投入档位改目标数</t>
+          <t>**档位解锁**（v1.12 再加注改造后腾空）、按投入档位改目标数</t>
         </is>
       </c>
     </row>
@@ -4847,12 +4847,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>单体（悬红）/ AoE（清台）/ 大额头奖（爆机）/ 处决（截胡）</t>
+          <t>单体（悬红）/ AoE·自我成长（清台）/ 大额头奖（爆机）</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>处决（v1.15 过路费改格挡返金后腾空）</t>
         </is>
       </c>
     </row>
@@ -4864,12 +4864,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>基准（筹码）/ 免能量（本钱）/ 投资回本（派彩）/ 掷币（抽头）/ 牌换金（兑筹）/ 贷款（高利贷）/ 弃牌堆（散码）/ 敌人数（买码）/ 手牌数（抽水）/ 手牌换金（清码）/ 破盾转金（吃水）/ 牌换金·小额（洗牌）</t>
+          <t>基准（筹码）/ 免能量（本钱）/ 投资回本（派彩）/ 掷币（抽头）/ 贷款（高利贷）/ 弃牌堆（捡漏）/ 敌人数（人头费）/ 手牌数（数牌）/ 手牌换金（清仓）/ 破盾转金（抽税）/ 牌换金·小额（典当）/ 掷币·高方差（翻本）/ 消耗堆（回收）</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>按生命值、按回合数、多次掷产金（老虎机，v1.8 腾空）</t>
+          <t>按生命值、按回合数、**多次掷产金（老虎机，v1.8 腾空）**</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>定额（返水）/ 正面触发（台规）/ 增幅（利滚利）/ 买血（分红，金→HP）</t>
+          <t>定额（返水）/ 正面触发（保护费）/ 增幅（利滚利）/ 买血（分红，金→HP）/ 借贷利息（高利贷）/ 产金转甲（存钱）</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>转伤害（连续下注）/ 回响·每金 +1 伤（加注）/ 转抽牌（流水）/ 转格挡（点码）/ 转能量（加码）</t>
+          <t>追加伤害（连续下注）/ 每金 +1 伤（加注）/ 转抽牌（流水）/ 转格挡（记账）/ 转敏捷（保本）</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>花费达标触发临时强化</t>
+          <t>花费达标触发临时强化、转能量（底气 v1.14 改为持有量）</t>
         </is>
       </c>
     </row>
@@ -4915,12 +4915,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>基础（试手气）/ AoE（买定离手）/ 格挡（盲注）/ 双段（双倍下注）/ 尖刺（翻本）/ 随机多段（摇骰）/ 反向（保险）/ 格挡反击（反水）</t>
+          <t>基础（试手气）/ AoE（买定离手）/ 格挡（跟注）/ 格挡·高投入（保险）/ 双段（双倍下注）/ 高方差产金（翻本）/ 随机多段（摇骰）/ 格挡反击（还手）</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>赌博·反伤护体、赌博·复制手牌、多掷/连锁/逐击（v1.8 随豹子/老虎机/连庄/连胜删除而腾空）</t>
+          <t>赌博·反伤护体、赌博·复制手牌、**多掷/连锁/逐击（v1.8 随豹子/老虎机/连庄/连胜删除而腾空）**</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>必正（暗记）/ 被动概率（手气正旺）/ 终极全正（赌神）/ 倍率注入（叠码）/ 倍率翻倍（倍投）/ 本回合全正（出千）</t>
+          <t>必正（暗记）/ 被动概率（手气正旺）/ 终极全正（赌神）/ 倍率注入（加码）/ 倍率翻倍（倍投）/ 本回合全正（出千）</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>尖刺（孤注一掷）/ 自伤多段（俄罗斯轮盘）/ 能量（单双）/ 押 HP（押宝）/ 押手牌（押牌）</t>
+          <t>尖刺（孤注一掷）/ 押 HP（押宝）/ 退注（押注）</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>兑现·格挡（收手）/ 单体（乘胜）/ 产金（兑现）/ AoE（通杀）/ 大炮（晒冷）/ 击杀续风（追数）/ 自伤（割肉）/ 终结（同花顺）/ 折算·抽牌（割禾青）/ 折算·能量（换筹）/ 只读条件（叠注、底牌）</t>
+          <t>兑现·格挡（收手/止损）/ 单体（乘胜）/ 产金（兑现）/ AoE（通杀）/ 击杀续风（追击）/ 终结（同花顺）/ 折算·抽牌（见好就收）/ 折算·能量（提现）/ 只读条件（叠注、底牌）</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>费用豁免（假筹）/ 自消耗换值（弃牌）/ 信息（数牌）/ 定向斩杀（打庄）/ 力量剥夺（抽佣）/ 消耗换抽（换牌）/ 消耗堆协同·格挡（保底）/ 生命条件（翻盘）/ 卖血换甲（抵押）/ 金币转格挡（保本）/ 弃牌堆规模（摊牌）/ 赌博计数（满贯）</t>
+          <t>费用豁免（假币）/ 自消耗换值（弃牌）/ 定向斩杀·穷鬼翻倍（打庄）/ 力量剥夺（暗算）/ 重抽（换牌）/ 消耗堆协同·产金（回收）/ 生命条件（翻盘）/ 回牌换甲（留一手）/ 弃牌堆规模（摊牌）/ 赌博计数（满贯）/ 倍率奇偶（单双）/ 格挡返金（过路费）/ 随机轮盘（俄罗斯轮盘）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>28 攻 / 44 技 / 13 能（v1.15：轮盘/晒冷 攻→能、截胡 攻→技、保本 技→能）</t>
+          <t>28 攻 / 44 技 / 13 能（v1.15：轮盘/存钱 攻→能、过路费 攻→技、保本 技→能）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>17（本钱/筹码/悬红/清台/派彩/抽头/高利贷/爆机/散码/买码/清码/吃水/洗牌/翻本/数牌/保底/截胡）</t>
+          <t>17（本钱/筹码/悬红/清台/派彩/抽头/高利贷/爆机/捡漏/人头费/清仓/抽税/典当/翻本/数牌/回收/过路费）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3（返水/台规/利滚利）</t>
+          <t>3（返水/保护费/利滚利）</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2（孤注一掷/押宝；v1.15 单双与轮盘去赌博化、押牌改退注后缩减）</t>
+          <t>2（孤注一掷/押宝；v1.15 单双与轮盘去赌博化、押注（原押牌）改退注后缩减）</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>8（遗物/暗记/手气正旺/赌神/叠码/倍投/出千/底牌-条件）</t>
+          <t>8（遗物/暗记/手气正旺/赌神/加码/倍投/出千/底牌-条件）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9 挂词条（7 + 同花顺 + 换筹）＋ 2 只读条件（叠注/底牌）</t>
+          <t>9 挂词条（7 + 同花顺 + 提现）＋ 2 只读条件（叠注/底牌）</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>28 攻 / 44 技 / 13 能（v1.15：轮盘/存钱 攻→能、过路费 攻→技、保本 技→能）</t>
+          <t>27 攻 / 45 技 / 13 能（v1.15：轮盘/存钱 攻→能、过路费 攻→技、保本 技→能）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">

--- a/docs/design/gambler-design.xlsx
+++ b/docs/design/gambler-design.xlsx
@@ -4690,21 +4690,181 @@
       <c r="B86" s="5" t="n">
         <v>86</v>
       </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>拼命</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>赌命·伤害加成</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>你造成的伤害 +「已失去生命」的 10%</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="B87" s="5" t="n">
         <v>87</v>
       </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>千王</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>出千·正面转必正</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>每回合前 1 次掷出正面时，获得 1 次必正</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>前 2 次</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="B88" s="5" t="n">
         <v>88</v>
       </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>瞒天过海</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>1能+6金</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>出千·本回合全正</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>本回合你接下来的 3 次赌博必为正面</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>4 次</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="B89" s="5" t="n">
         <v>89</v>
       </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>赌命</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>2能+10金</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>赌命·血线大炮</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>造成「已失去生命」50% 的伤害</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
     </row>
     <row r="90"/>
     <row r="91">
@@ -4751,14 +4911,10 @@
     </row>
   </sheetData>
   <autoFilter ref="B4:J49"/>
-  <mergeCells count="7">
-    <mergeCell ref="B87:J87"/>
+  <mergeCells count="3">
     <mergeCell ref="B90:J90"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="B88:J88"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B91:J91"/>
-    <mergeCell ref="B86:J86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
